--- a/context_DB/NER_context_db.xlsx
+++ b/context_DB/NER_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM50"/>
+  <dimension ref="A1:BN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -691,65 +691,70 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>fatalities</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>event_count_evt2</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>ADM1_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>ADM3_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sub_event_type</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>actor1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_1</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>actor2</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_2</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
           <t>admin2</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>fatalities</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>event_count_evt2</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>ADM3_PCODE_evt2</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>sub_event_type</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>actor1</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_1</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>actor2</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_2</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>ratio IDP/ToTN - HPC2025</t>
         </is>
@@ -772,7 +777,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE003006;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -866,7 +871,8 @@
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="n">
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="n">
         <v>0.07240645575718645</v>
       </c>
     </row>
@@ -887,7 +893,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE003006;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -973,16 +979,16 @@
           <t>Diffa</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>Diffa</t>
-        </is>
+      <c r="BA3" t="n">
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
         <v>1</v>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>NE002</t>
+        </is>
       </c>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr">
@@ -1014,10 +1020,15 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>29 April 2024</t>
-        </is>
-      </c>
-      <c r="BM3" t="n">
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>Diffa</t>
+        </is>
+      </c>
+      <c r="BN3" t="n">
         <v>0.2579604477852696</v>
       </c>
     </row>
@@ -1038,7 +1049,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE003006;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1132,7 +1143,8 @@
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="n">
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="n">
         <v>0.001071480459102136</v>
       </c>
     </row>
@@ -1247,7 +1259,8 @@
       <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="n">
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="n">
         <v>0.09055399608071607</v>
       </c>
     </row>
@@ -1268,7 +1281,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1362,7 +1375,8 @@
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="n">
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1477,7 +1491,8 @@
       <c r="BJ7" t="inlineStr"/>
       <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="n">
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="n">
         <v>0.4003178206583428</v>
       </c>
     </row>
@@ -1498,7 +1513,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1592,7 +1607,8 @@
       <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="n">
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1613,7 +1629,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NE003002;NE003003;NE003004;NE003005</t>
+          <t>NE003002;NE003003;NE003005</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1707,7 +1723,8 @@
       <c r="BJ9" t="inlineStr"/>
       <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="n">
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1728,7 +1745,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NE003002;NE003003;NE003004;NE003005</t>
+          <t>NE003002;NE003003;NE003005</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1814,16 +1831,16 @@
           <t>Dosso</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>Dogondoutchi</t>
-        </is>
+      <c r="BA10" t="n">
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
         <v>1</v>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>NE003</t>
+        </is>
       </c>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr">
@@ -1859,10 +1876,15 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>17 March 2024</t>
-        </is>
-      </c>
-      <c r="BM10" t="n">
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>Dogondoutchi</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
         <v>0.002268536887063272</v>
       </c>
     </row>
@@ -1878,12 +1900,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NE003002</t>
+          <t>NE003004</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NE003002;NE003003;NE003004;NE003005</t>
+          <t>NE003004</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1969,36 +1991,36 @@
           <t>Dosso</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>Dosso</t>
-        </is>
+      <c r="BA11" t="n">
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
         <v>2</v>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>NE003</t>
+        </is>
       </c>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>Protests ---- Riots</t>
+          <t>Riots ---- Protests</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Violent demonstration</t>
+          <t>Violent demonstration ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Protesters (Niger) ---- Rioters (Niger)</t>
+          <t>Rioters (Niger) ---- Protesters (Niger)</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>SYNACEB: National Union of Contract Agents and Basic Education Officers; Teachers (Niger) ---- Students (Niger)</t>
+          <t>Students (Niger) ---- SYNACEB: National Union of Contract Agents and Basic Education Officers; Teachers (Niger)</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -2009,15 +2031,20 @@
       <c r="BJ11" t="inlineStr"/>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>On 24 March 2025, contractual teachers from the National Union of Contractual Agents and Civil Servants in Basic Education (SYNACEB) organized a sit-in in front of the governorate in Dosso (Dosso, Dosso) to denounce irregularities in the payment of their wages. ---- On 14 October 2024, students clashed with police forces near the university in Dosso (Dosso, Dosso). The students were marching towards the governorate to demand a response to previous incidents involving security forces. Clashes erupted when security forces used tear gas to disperse the crowd. Students responded by throwing stones, erecting barricades, and setting fire to the main road in front of the campus. Casualties unknown.</t>
+          <t>On 14 October 2024, students clashed with police forces near the university in Dosso (Dosso, Dosso). The students were marching towards the governorate to demand a response to previous incidents involving security forces. Clashes erupted when security forces used tear gas to disperse the crowd. Students responded by throwing stones, erecting barricades, and setting fire to the main road in front of the campus. Casualties unknown. ---- On 24 March 2025, contractual teachers from the National Union of Contractual Agents and Civil Servants in Basic Education (SYNACEB) organized a sit-in in front of the governorate in Dosso (Dosso, Dosso) to denounce irregularities in the payment of their wages.</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>24 March 2025 ---- 14 October 2024</t>
-        </is>
-      </c>
-      <c r="BM11" t="n">
+          <t>2024-10-14 ---- 2025-03-24</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>Dosso</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2038,7 +2065,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NE003002;NE003003;NE003004;NE003005</t>
+          <t>NE003002;NE003003;NE003005</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2132,7 +2159,8 @@
       <c r="BJ12" t="inlineStr"/>
       <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="n">
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2148,12 +2176,12 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NE002001</t>
+          <t>NE006009</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE003006;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2247,7 +2275,8 @@
       <c r="BJ13" t="inlineStr"/>
       <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="n">
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="n">
         <v>0.00683120024454102</v>
       </c>
     </row>
@@ -2268,7 +2297,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NE003007;NE004003;NE004007;NE005002;NE005007;NE005010;NE006001;NE006006;NE006010</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2354,16 +2383,16 @@
           <t>Dosso</t>
         </is>
       </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>Loga</t>
-        </is>
+      <c r="BA14" t="n">
+        <v>1</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
       </c>
-      <c r="BC14" t="n">
-        <v>1</v>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>NE003</t>
+        </is>
       </c>
       <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="inlineStr">
@@ -2399,10 +2428,15 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>13 April 2025</t>
-        </is>
-      </c>
-      <c r="BM14" t="n">
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>Loga</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2517,7 +2551,8 @@
       <c r="BJ15" t="inlineStr"/>
       <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr"/>
-      <c r="BM15" t="n">
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2538,7 +2573,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE003006;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2632,7 +2667,8 @@
       <c r="BJ16" t="inlineStr"/>
       <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="n">
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2653,7 +2689,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE003006;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2747,7 +2783,8 @@
       <c r="BJ17" t="inlineStr"/>
       <c r="BK17" t="inlineStr"/>
       <c r="BL17" t="inlineStr"/>
-      <c r="BM17" t="n">
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2768,7 +2805,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NE003007;NE004003;NE004007;NE005002;NE005007;NE005010;NE006001;NE006006;NE006010</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2862,7 +2899,8 @@
       <c r="BJ18" t="inlineStr"/>
       <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="inlineStr"/>
-      <c r="BM18" t="n">
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2883,7 +2921,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2977,7 +3015,8 @@
       <c r="BJ19" t="inlineStr"/>
       <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr"/>
-      <c r="BM19" t="n">
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3092,7 +3131,8 @@
       <c r="BJ20" t="inlineStr"/>
       <c r="BK20" t="inlineStr"/>
       <c r="BL20" t="inlineStr"/>
-      <c r="BM20" t="n">
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="n">
         <v>0.01211911571222968</v>
       </c>
     </row>
@@ -3113,7 +3153,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE003006;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3207,7 +3247,8 @@
       <c r="BJ21" t="inlineStr"/>
       <c r="BK21" t="inlineStr"/>
       <c r="BL21" t="inlineStr"/>
-      <c r="BM21" t="n">
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="n">
         <v>0.01035549276413762</v>
       </c>
     </row>
@@ -3228,7 +3269,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NE003007;NE004003;NE004007;NE005002;NE005007;NE005010;NE006001;NE006006;NE006010</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3314,16 +3355,16 @@
           <t>Maradi</t>
         </is>
       </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>Ville de Maradi</t>
-        </is>
+      <c r="BA22" t="n">
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
         <v>2</v>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>NE004</t>
+        </is>
       </c>
       <c r="BD22" t="inlineStr"/>
       <c r="BE22" t="inlineStr">
@@ -3343,22 +3384,27 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>Students (Niger); USN: Union of Nigerien Students ---- Muslim Group (Niger)</t>
+          <t>Muslim Group (Niger) ---- Students (Niger); USN: Union of Nigerien Students</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr"/>
       <c r="BJ22" t="inlineStr"/>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>On 29 April 2024, thousands of students including members of the USN staged a demonstration in Maradi (Ville de Maradi, Maradi) in support of the National Council for the Safeguarding of the Homeland (CNSP) decision to expel all foreign forces from Niger. ---- On 5 April 2024, many residents carrying Palestinian flags demonstrated in support for Palestine in Maradi (Ville de Maradi, Maradi). The protest was organized by a few Koranic schools of Shiite obedience.</t>
+          <t>On 5 April 2024, many residents carrying Palestinian flags demonstrated in support for Palestine in Maradi (Ville de Maradi, Maradi). The protest was organized by a few Koranic schools of Shiite obedience. ---- On 29 April 2024, thousands of students including members of the USN staged a demonstration in Maradi (Ville de Maradi, Maradi) in support of the National Council for the Safeguarding of the Homeland (CNSP) decision to expel all foreign forces from Niger.</t>
         </is>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>29 April 2024 ---- 05 April 2024</t>
-        </is>
-      </c>
-      <c r="BM22" t="n">
+          <t>2024-04-05 ---- 2024-04-29</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>Ville de Maradi</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3379,7 +3425,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3473,7 +3519,8 @@
       <c r="BJ23" t="inlineStr"/>
       <c r="BK23" t="inlineStr"/>
       <c r="BL23" t="inlineStr"/>
-      <c r="BM23" t="n">
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3588,7 +3635,8 @@
       <c r="BJ24" t="inlineStr"/>
       <c r="BK24" t="inlineStr"/>
       <c r="BL24" t="inlineStr"/>
-      <c r="BM24" t="n">
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3703,7 +3751,8 @@
       <c r="BJ25" t="inlineStr"/>
       <c r="BK25" t="inlineStr"/>
       <c r="BL25" t="inlineStr"/>
-      <c r="BM25" t="n">
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3724,7 +3773,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>NE003007;NE004003;NE004007;NE005002;NE005007;NE005010;NE006001;NE006006;NE006010</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3818,7 +3867,8 @@
       <c r="BJ26" t="inlineStr"/>
       <c r="BK26" t="inlineStr"/>
       <c r="BL26" t="inlineStr"/>
-      <c r="BM26" t="n">
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="n">
         <v>0.05348192126137525</v>
       </c>
     </row>
@@ -3933,7 +3983,8 @@
       <c r="BJ27" t="inlineStr"/>
       <c r="BK27" t="inlineStr"/>
       <c r="BL27" t="inlineStr"/>
-      <c r="BM27" t="n">
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3954,7 +4005,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4048,7 +4099,8 @@
       <c r="BJ28" t="inlineStr"/>
       <c r="BK28" t="inlineStr"/>
       <c r="BL28" t="inlineStr"/>
-      <c r="BM28" t="n">
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4069,7 +4121,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4163,7 +4215,8 @@
       <c r="BJ29" t="inlineStr"/>
       <c r="BK29" t="inlineStr"/>
       <c r="BL29" t="inlineStr"/>
-      <c r="BM29" t="n">
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4184,7 +4237,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4278,7 +4331,8 @@
       <c r="BJ30" t="inlineStr"/>
       <c r="BK30" t="inlineStr"/>
       <c r="BL30" t="inlineStr"/>
-      <c r="BM30" t="n">
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4299,7 +4353,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NE003007;NE004003;NE004007;NE005002;NE005007;NE005010;NE006001;NE006006;NE006010</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4393,7 +4447,8 @@
       <c r="BJ31" t="inlineStr"/>
       <c r="BK31" t="inlineStr"/>
       <c r="BL31" t="inlineStr"/>
-      <c r="BM31" t="n">
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="n">
         <v>0.005652259671096427</v>
       </c>
     </row>
@@ -4414,7 +4469,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4508,7 +4563,8 @@
       <c r="BJ32" t="inlineStr"/>
       <c r="BK32" t="inlineStr"/>
       <c r="BL32" t="inlineStr"/>
-      <c r="BM32" t="n">
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4689,7 +4745,8 @@
       <c r="BJ33" t="inlineStr"/>
       <c r="BK33" t="inlineStr"/>
       <c r="BL33" t="inlineStr"/>
-      <c r="BM33" t="n">
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="n">
         <v>0.00642803895929316</v>
       </c>
     </row>
@@ -4710,7 +4767,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NE003007;NE004003;NE004007;NE005002;NE005007;NE005010;NE006001;NE006006;NE006010</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -4804,7 +4861,8 @@
       <c r="BJ34" t="inlineStr"/>
       <c r="BK34" t="inlineStr"/>
       <c r="BL34" t="inlineStr"/>
-      <c r="BM34" t="n">
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="n">
         <v>0.5016542002301496</v>
       </c>
     </row>
@@ -4825,7 +4883,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NE005011;NE005012;NE006007;NE006009</t>
+          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4919,7 +4977,8 @@
       <c r="BJ35" t="inlineStr"/>
       <c r="BK35" t="inlineStr"/>
       <c r="BL35" t="inlineStr"/>
-      <c r="BM35" t="n">
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="n">
         <v>0.01920465567410281</v>
       </c>
     </row>
@@ -4940,7 +4999,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NE005011;NE005012;NE006007;NE006009</t>
+          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -5026,16 +5085,16 @@
           <t>Tahoua</t>
         </is>
       </c>
-      <c r="BA36" t="inlineStr">
-        <is>
-          <t>Tillia</t>
-        </is>
+      <c r="BA36" t="n">
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
         <v>1</v>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>NE005</t>
+        </is>
       </c>
       <c r="BD36" t="inlineStr"/>
       <c r="BE36" t="inlineStr">
@@ -5071,10 +5130,15 @@
       </c>
       <c r="BL36" t="inlineStr">
         <is>
-          <t>04 February 2024</t>
-        </is>
-      </c>
-      <c r="BM36" t="n">
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="BM36" t="inlineStr">
+        <is>
+          <t>Tillia</t>
+        </is>
+      </c>
+      <c r="BN36" t="n">
         <v>0.2978905359179019</v>
       </c>
     </row>
@@ -5181,16 +5245,16 @@
           <t>Tahoua</t>
         </is>
       </c>
-      <c r="BA37" t="inlineStr">
-        <is>
-          <t>Ville de Tahoua</t>
-        </is>
+      <c r="BA37" t="n">
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC37" t="n">
         <v>2</v>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>NE005</t>
+        </is>
       </c>
       <c r="BD37" t="inlineStr"/>
       <c r="BE37" t="inlineStr">
@@ -5210,22 +5274,27 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>ITN: Inter-union of Workers of Niger; Labor Group (Niger); SNEB: National Union of the Teachers of Basic education; Teachers (Niger) ---- Students (Niger); USN: Union of Nigerien Students</t>
+          <t>Students (Niger); USN: Union of Nigerien Students ---- ITN: Inter-union of Workers of Niger; Labor Group (Niger); SNEB: National Union of the Teachers of Basic education; Teachers (Niger)</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr"/>
       <c r="BJ37" t="inlineStr"/>
       <c r="BK37" t="inlineStr">
         <is>
-          <t>On 1 May 2025, at the call of unions (ITN, SNEB), workers demonstrated in Tahoua (Ville de Tahoua, Tahoua) to commemorate International Workers' Day. They called for the improvement of the working and living conditions for Niger's workers. ---- On 29 April 2024, thousands of students including members of the USN staged a demonstration in Tahoua (Ville de Tahoua, Tahoua). The protesters demanded the revision of all mining and oil agreements and the closure of all foreign bases in Niger.</t>
+          <t>On 29 April 2024, thousands of students including members of the USN staged a demonstration in Tahoua (Ville de Tahoua, Tahoua). The protesters demanded the revision of all mining and oil agreements and the closure of all foreign bases in Niger. ---- On 1 May 2025, at the call of unions (ITN, SNEB), workers demonstrated in Tahoua (Ville de Tahoua, Tahoua) to commemorate International Workers' Day. They called for the improvement of the working and living conditions for Niger's workers.</t>
         </is>
       </c>
       <c r="BL37" t="inlineStr">
         <is>
-          <t>01 May 2025 ---- 29 April 2024</t>
-        </is>
-      </c>
-      <c r="BM37" t="n">
+          <t>2024-04-29 ---- 2025-05-01</t>
+        </is>
+      </c>
+      <c r="BM37" t="inlineStr">
+        <is>
+          <t>Ville de Tahoua</t>
+        </is>
+      </c>
+      <c r="BN37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5246,7 +5315,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NE003007;NE004003;NE004007;NE005002;NE005007;NE005010;NE006001;NE006006;NE006010</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5332,16 +5401,16 @@
           <t>Tillaberi</t>
         </is>
       </c>
-      <c r="BA38" t="inlineStr">
-        <is>
-          <t>Abala</t>
-        </is>
+      <c r="BA38" t="n">
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" t="n">
         <v>1</v>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
       </c>
       <c r="BD38" t="inlineStr"/>
       <c r="BE38" t="inlineStr">
@@ -5377,10 +5446,15 @@
       </c>
       <c r="BL38" t="inlineStr">
         <is>
-          <t>17 January 2024</t>
-        </is>
-      </c>
-      <c r="BM38" t="n">
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="BM38" t="inlineStr">
+        <is>
+          <t>Abala</t>
+        </is>
+      </c>
+      <c r="BN38" t="n">
         <v>0.07642879415564167</v>
       </c>
     </row>
@@ -5495,7 +5569,8 @@
       <c r="BJ39" t="inlineStr"/>
       <c r="BK39" t="inlineStr"/>
       <c r="BL39" t="inlineStr"/>
-      <c r="BM39" t="n">
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="n">
         <v>0.2286097636494994</v>
       </c>
     </row>
@@ -5516,7 +5591,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5610,7 +5685,8 @@
       <c r="BJ40" t="inlineStr"/>
       <c r="BK40" t="inlineStr"/>
       <c r="BL40" t="inlineStr"/>
-      <c r="BM40" t="n">
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="n">
         <v>0.01764771943334777</v>
       </c>
     </row>
@@ -5631,7 +5707,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE004004;NE004008;NE005004;NE005005;NE005006;NE005008;NE006003;NE006004</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5725,7 +5801,8 @@
       <c r="BJ41" t="inlineStr"/>
       <c r="BK41" t="inlineStr"/>
       <c r="BL41" t="inlineStr"/>
-      <c r="BM41" t="n">
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="n">
         <v>0.1041051577623168</v>
       </c>
     </row>
@@ -5840,7 +5917,8 @@
       <c r="BJ42" t="inlineStr"/>
       <c r="BK42" t="inlineStr"/>
       <c r="BL42" t="inlineStr"/>
-      <c r="BM42" t="n">
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="n">
         <v>0.02472110303496589</v>
       </c>
     </row>
@@ -5861,7 +5939,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NE003007;NE004003;NE004007;NE005002;NE005007;NE005010;NE006001;NE006006;NE006010</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5955,7 +6033,8 @@
       <c r="BJ43" t="inlineStr"/>
       <c r="BK43" t="inlineStr"/>
       <c r="BL43" t="inlineStr"/>
-      <c r="BM43" t="n">
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="n">
         <v>0.0187722395001541</v>
       </c>
     </row>
@@ -5976,7 +6055,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>NE005011;NE005012;NE006007;NE006009</t>
+          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6062,16 +6141,16 @@
           <t>Tillaberi</t>
         </is>
       </c>
-      <c r="BA44" t="inlineStr">
-        <is>
-          <t>Gotheye</t>
-        </is>
+      <c r="BA44" t="n">
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC44" t="n">
         <v>3</v>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
       </c>
       <c r="BD44" t="inlineStr"/>
       <c r="BE44" t="inlineStr">
@@ -6102,15 +6181,20 @@
       </c>
       <c r="BK44" t="inlineStr">
         <is>
-          <t>Property destruction: On 25 April 2024, likely JNIM militants set classrooms of a school on fire in the village of Bangou Tara (Gotheye, Tillaberi). There were no casualties but several school equipment were destroyed. Alerted, an FDS unit managed to control the fire and launch an unsuccessful pursuit. ---- Property destruction: On 25 April 2024, JNIM fighters burned classrooms of a primary school during an incursion in the village of Bangou Karey Koulbaga (Gotheye, Tillaberi). ---- Property destruction: On 15 April 2024, JNIM militants set some classrooms of a primary school on fire in the village of Dina (Gotheye, Tillaberi) during an incursion. Before withdrawing, the militants stole food from the school canteen.</t>
+          <t>Property destruction: On 15 April 2024, JNIM militants set some classrooms of a primary school on fire in the village of Dina (Gotheye, Tillaberi) during an incursion. Before withdrawing, the militants stole food from the school canteen. ---- Property destruction: On 25 April 2024, likely JNIM militants set classrooms of a school on fire in the village of Bangou Tara (Gotheye, Tillaberi). There were no casualties but several school equipment were destroyed. Alerted, an FDS unit managed to control the fire and launch an unsuccessful pursuit. ---- Property destruction: On 25 April 2024, JNIM fighters burned classrooms of a primary school during an incursion in the village of Bangou Karey Koulbaga (Gotheye, Tillaberi).</t>
         </is>
       </c>
       <c r="BL44" t="inlineStr">
         <is>
-          <t>25 April 2024 ---- 25 April 2024 ---- 15 April 2024</t>
-        </is>
-      </c>
-      <c r="BM44" t="n">
+          <t>2024-04-15 ---- 2024-04-25 ---- 2024-04-25</t>
+        </is>
+      </c>
+      <c r="BM44" t="inlineStr">
+        <is>
+          <t>Gotheye</t>
+        </is>
+      </c>
+      <c r="BN44" t="n">
         <v>0.05534044965452328</v>
       </c>
     </row>
@@ -6225,7 +6309,8 @@
       <c r="BJ45" t="inlineStr"/>
       <c r="BK45" t="inlineStr"/>
       <c r="BL45" t="inlineStr"/>
-      <c r="BM45" t="n">
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="n">
         <v>0.0004394825185672131</v>
       </c>
     </row>
@@ -6246,7 +6331,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>NE005011;NE005012;NE006007;NE006009</t>
+          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6332,16 +6417,16 @@
           <t>Tillaberi</t>
         </is>
       </c>
-      <c r="BA46" t="inlineStr">
-        <is>
-          <t>Ouallam</t>
-        </is>
+      <c r="BA46" t="n">
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
         <v>1</v>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
       </c>
       <c r="BD46" t="inlineStr"/>
       <c r="BE46" t="inlineStr">
@@ -6377,10 +6462,15 @@
       </c>
       <c r="BL46" t="inlineStr">
         <is>
-          <t>19 April 2024</t>
-        </is>
-      </c>
-      <c r="BM46" t="n">
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="BM46" t="inlineStr">
+        <is>
+          <t>Ouallam</t>
+        </is>
+      </c>
+      <c r="BN46" t="n">
         <v>0.01943990737486303</v>
       </c>
     </row>
@@ -6401,7 +6491,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NE003007;NE004003;NE004007;NE005002;NE005007;NE005010;NE006001;NE006006;NE006010</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6482,20 +6572,65 @@
       <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="inlineStr"/>
       <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="inlineStr"/>
-      <c r="BB47" t="inlineStr"/>
-      <c r="BC47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>Tillaberi</t>
+        </is>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
+      </c>
       <c r="BD47" t="inlineStr"/>
-      <c r="BE47" t="inlineStr"/>
-      <c r="BF47" t="inlineStr"/>
-      <c r="BG47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction</t>
+        </is>
+      </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
+        </is>
+      </c>
       <c r="BH47" t="inlineStr"/>
-      <c r="BI47" t="inlineStr"/>
-      <c r="BJ47" t="inlineStr"/>
-      <c r="BK47" t="inlineStr"/>
-      <c r="BL47" t="inlineStr"/>
-      <c r="BM47" t="n">
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger)</t>
+        </is>
+      </c>
+      <c r="BJ47" t="inlineStr">
+        <is>
+          <t>Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger)</t>
+        </is>
+      </c>
+      <c r="BK47" t="inlineStr">
+        <is>
+          <t>Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of Loudia Banda (Say, Tillaberi), Dokimana, Dyongore and 'Seckere' (coded separately). ---- Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of Dokimana (Say, Tillaberi), Loudia Banda, Dyongore and 'Seckere' (coded separately). ---- Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of Dyongore (Say, Tillaberi), Dokimana, Loudia Banda and 'Seckere' (coded separately). ---- Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of 'Seckere', in the area of Say (Say, Tillaberi), Loudia Banda, Dokimana and Dyongore (coded separately).</t>
+        </is>
+      </c>
+      <c r="BL47" t="inlineStr">
+        <is>
+          <t>2024-12-18 ---- 2024-12-18 ---- 2024-12-18 ---- 2024-12-18</t>
+        </is>
+      </c>
+      <c r="BM47" t="inlineStr">
+        <is>
+          <t>Say</t>
+        </is>
+      </c>
+      <c r="BN47" t="n">
         <v>0.03474261107848894</v>
       </c>
     </row>
@@ -6602,16 +6737,16 @@
           <t>Tillaberi</t>
         </is>
       </c>
-      <c r="BA48" t="inlineStr">
-        <is>
-          <t>Tera</t>
-        </is>
+      <c r="BA48" t="n">
+        <v>1</v>
       </c>
       <c r="BB48" t="n">
         <v>1</v>
       </c>
-      <c r="BC48" t="n">
-        <v>1</v>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
       </c>
       <c r="BD48" t="inlineStr"/>
       <c r="BE48" t="inlineStr">
@@ -6643,10 +6778,15 @@
       </c>
       <c r="BL48" t="inlineStr">
         <is>
-          <t>20 December 2024</t>
-        </is>
-      </c>
-      <c r="BM48" t="n">
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="BM48" t="inlineStr">
+        <is>
+          <t>Tera</t>
+        </is>
+      </c>
+      <c r="BN48" t="n">
         <v>0.06796245552329148</v>
       </c>
     </row>
@@ -6753,16 +6893,16 @@
           <t>Tillaberi</t>
         </is>
       </c>
-      <c r="BA49" t="inlineStr">
-        <is>
-          <t>Tillaberi</t>
-        </is>
+      <c r="BA49" t="n">
+        <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC49" t="n">
         <v>1</v>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
       </c>
       <c r="BD49" t="inlineStr"/>
       <c r="BE49" t="inlineStr">
@@ -6794,10 +6934,15 @@
       </c>
       <c r="BL49" t="inlineStr">
         <is>
-          <t>01 May 2025</t>
-        </is>
-      </c>
-      <c r="BM49" t="n">
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="BM49" t="inlineStr">
+        <is>
+          <t>Tillaberi</t>
+        </is>
+      </c>
+      <c r="BN49" t="n">
         <v>0.0665961065961066</v>
       </c>
     </row>
@@ -6818,7 +6963,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE003006;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -6904,55 +7049,60 @@
           <t>Tillaberi</t>
         </is>
       </c>
-      <c r="BA50" t="inlineStr">
-        <is>
-          <t>Torodi</t>
-        </is>
+      <c r="BA50" t="n">
+        <v>11</v>
       </c>
       <c r="BB50" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
       </c>
       <c r="BD50" t="inlineStr"/>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Strategic developments</t>
+          <t>Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Strategic developments ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>Attack ---- Looting/property destruction</t>
+          <t>Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Attack ---- Looting/property destruction ---- Attack</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
+          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr"/>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Civilians (Niger) ---- Civilians (Niger)</t>
+          <t>Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger)</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr">
         <is>
-          <t>Labor Group (Niger)</t>
+          <t>Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Teachers (Niger); Students (Niger) ---- Students (Niger); Teachers (Niger) ---- Muslim Group (Niger); Students (Niger); Teachers (Niger) ---- Labor Group (Niger) ---- Students (Niger); Teachers (Niger) ---- Teachers (Niger); SYNACEB: National Union of Contract Agents and Basic Education Officers</t>
         </is>
       </c>
       <c r="BK50" t="inlineStr">
         <is>
-          <t>On 1 May 2025, armed militants (likely JNIM, based on location) raided Makalondi (Makalondi, Torodi, Tillaberi), killing the president of the city's Schools Management Committee (COGES) and a trader. ---- Property destruction: Around 20 January 2025 (between 19 - 22 January), an armed group (likely JNIM, based on the location) set fire to five classrooms in Djoga (Torodi, Tillaberi). They also fired shots in the air.</t>
+          <t>Property destruction: On 18 January 2025, overnight, armed militants (likely JNIM, based on location) burned down the school of 'Bogodjoti', a few kilometers north-west of Torodi, code to Kobio (Torodi, Tillaberi), a representative location in the area. ---- Property destruction: Around 20 January 2025 (between 19 - 22 January), an armed group (likely JNIM, based on the location) set fire to five classrooms in Djoga (Torodi, Tillaberi). They also fired shots in the air. ---- Property destruction: On 30 January 2025, JNIM militants burned down a school in the periphery of Torodi (Torodi, Tillaberi). ---- Property destruction: On 2 February 2025, JNIM militants burned down the school of Sirimbana (Torodi, Tillaberi). ---- Property destruction: On 11 February 2025, overnight, JNIM militants burned down the primary school of Tikko (Torodi, Tillaberi). ---- Property destruction: On 11 February 2025, overnight, JNIM militants burned down the primary school of 'Winde Silloube', coded to Kobadje (Torodi, Tillaberi), a representative center in the area. ---- Property destruction: On 11 February 2025, overnight, JNIM militants burned down the primary school, the middle school and the Quranic school of Kobadje (Torodi, Tillaberi). ---- On 1 May 2025, armed militants (likely JNIM, based on location) raided Makalondi (Makalondi, Torodi, Tillaberi), killing the president of the city's Schools Management Committee (COGES) and a trader. ---- Property destruction: On 16 May 2025, overnight, armed militants (likely JNIM, based on location) set fire to several schools of Kobadje (Torodi, Tillaberi). ---- On 13 June 2025, JNIM attacked a passenger vehicle between Makalondi and Torodi, coded to Niakatire (Torodi, Tillaberi), a middle point between the two locations, killing 9 civilians and injuring others. The National Union of Contract Agents and Basic Education Officers (SYNACEB) confirmed the death toll, adding that during the attack, SYNACEB members, a teacher of 'Banira' elementary school was killed and a teacher of Patti elementary school was seriously injured and evacuated to Niamey.</t>
         </is>
       </c>
       <c r="BL50" t="inlineStr">
         <is>
-          <t>01 May 2025 ---- 20 January 2025</t>
-        </is>
-      </c>
-      <c r="BM50" t="n">
+          <t>2025-01-18 ---- 2025-01-20 ---- 2025-01-30 ---- 2025-02-02 ---- 2025-02-11 ---- 2025-02-11 ---- 2025-02-11 ---- 2025-05-01 ---- 2025-05-16 ---- 2025-06-13</t>
+        </is>
+      </c>
+      <c r="BM50" t="inlineStr">
+        <is>
+          <t>Torodi</t>
+        </is>
+      </c>
+      <c r="BN50" t="n">
         <v>0.1575871091617567</v>
       </c>
     </row>
@@ -6962,10 +7112,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9824523CAB29F4DA646F20BAFE41B4C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c972c102b01d47663811fb2ebdbd1e4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" xmlns:ns3="14cbb838-50ff-4dab-9c3f-cddf75f03c13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd0e8b72e466adcc572d3af37c1ebe05" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6"/>
-    <xsd:import namespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
+    <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <xsd:import namespace="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -6977,13 +7127,15 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
@@ -6992,7 +7144,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4877444-78fa-4cfa-bafc-d6c64fafc061" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -7010,52 +7162,57 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0fa6634-326e-4532-91a2-52bea7ac9212" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
@@ -7083,6 +7240,17 @@
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{d6bd4e25-e667-4943-8e38-5db701f530ee}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0fa6634-326e-4532-91a2-52bea7ac9212">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -7196,7 +7364,8 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5940141-1bc9-4c17-b1bc-e50f6b2083d6">
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
@@ -7204,13 +7373,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C697D6DC-9F15-429F-A881-4669ADF4D4EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE5C6610-D3B5-409C-8A75-591ED873AC3C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01730E41-C18C-4166-A22A-AFA9D402A62A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3594E97F-8102-4F75-B44D-F676BF6D94BA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8A02D15-B503-4BBF-9DCA-D4C1525DEBAC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECC02CCA-8BD5-440E-AF16-40B365B5E442}"/>
 </file>
--- a/context_DB/NER_context_db.xlsx
+++ b/context_DB/NER_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN50"/>
+  <dimension ref="A1:BN52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,74 +763,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NE002001</t>
+          <t>NE001002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NE002003</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>186.05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P2" t="n">
-        <v>13.53</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -858,28 +816,68 @@
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>Agadez</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>NE001</t>
+        </is>
+      </c>
       <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Disrupted weapons use</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Military Forces of Niger (2023-)</t>
+        </is>
+      </c>
       <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Niger)</t>
+        </is>
+      </c>
       <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>Defusal: Around 31 January 2025 (between 30 January - 1 February), military engineers defused a grenade left by an unidentified armed group in a school in Arlit (Arlit, Agadez).</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>Arlit</t>
+        </is>
+      </c>
       <c r="BN2" t="n">
-        <v>0.07240645575718645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NE002002</t>
+          <t>NE002001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -888,7 +886,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NE004001</t>
+          <t>NE002003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -897,55 +895,55 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>40.9</v>
+        <v>29</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>33.4</v>
       </c>
       <c r="M3" t="n">
-        <v>171.62</v>
+        <v>186.05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P3" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1.47</v>
       </c>
-      <c r="P3" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4.91</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>9.550000000000001</v>
+        <v>5.17</v>
       </c>
       <c r="T3" t="n">
-        <v>6.66</v>
+        <v>4.44</v>
       </c>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W3" t="n">
         <v>0.3</v>
       </c>
-      <c r="V3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.23</v>
-      </c>
       <c r="X3" t="n">
-        <v>0.3</v>
+        <v>0.93</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
@@ -974,68 +972,28 @@
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>Diffa</t>
-        </is>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>NE002</t>
-        </is>
-      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>Protests</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>Peaceful protest</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>Protesters (Niger)</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>Students (Niger); USN: Union of Nigerien Students</t>
-        </is>
-      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>On 29 April 2024, students members of the USN staged a demonstration in Diffa (Diffa, Diffa) in support of the National Council for the Safeguarding of the Homeland (CNSP) to continue the fight for the national sovereignty of Niger.</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>Diffa</t>
-        </is>
-      </c>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>0.2579604477852696</v>
+        <v>0.07240645575718645</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NE002003</t>
+          <t>NE002002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -1053,55 +1011,55 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>71.2</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
-        <v>19.6</v>
+        <v>40.9</v>
       </c>
       <c r="J4" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" t="n">
+        <v>171.62</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="U4" t="n">
         <v>0.3</v>
       </c>
-      <c r="L4" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>68.63</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="P4" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6.619999999999999</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="X4" t="n">
-        <v>1.32</v>
+        <v>0.3</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
@@ -1130,28 +1088,68 @@
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>Diffa</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>NE002</t>
+        </is>
+      </c>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Protesters (Niger)</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>Students (Niger); USN: Union of Nigerien Students</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>On 29 April 2024, students members of the USN staged a demonstration in Diffa (Diffa, Diffa) in support of the National Council for the Safeguarding of the Homeland (CNSP) to continue the fight for the national sovereignty of Niger.</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>Diffa</t>
+        </is>
+      </c>
       <c r="BN4" t="n">
-        <v>0.001071480459102136</v>
+        <v>0.2579604477852696</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NE002004</t>
+          <t>NE002003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1160,64 +1158,64 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NE005013</t>
+          <t>NE004001</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NE002004;NE002006;NE005013;NE006011</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>70.7</v>
+        <v>71.2</v>
       </c>
       <c r="I5" t="n">
-        <v>25.8</v>
+        <v>19.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>8.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L5" t="n">
-        <v>29.3</v>
+        <v>28.8</v>
       </c>
       <c r="M5" t="n">
-        <v>103.97</v>
+        <v>68.63</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>7.23</v>
+        <v>18.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.25</v>
+        <v>3.93</v>
       </c>
       <c r="R5" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.29</v>
+        <v>1.07</v>
       </c>
       <c r="T5" t="n">
-        <v>0.21</v>
+        <v>6.619999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8099999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
@@ -1261,13 +1259,13 @@
       <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
-        <v>0.09055399608071607</v>
+        <v>0.001071480459102136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NE002005</t>
+          <t>NE002004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -1276,64 +1274,64 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NE006004</t>
+          <t>NE005013</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE002004;NE002006;NE005013;NE006011</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>17.7</v>
+        <v>70.7</v>
       </c>
       <c r="I6" t="n">
-        <v>77.3</v>
+        <v>25.8</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L6" t="n">
-        <v>82.3</v>
+        <v>29.3</v>
       </c>
       <c r="M6" t="n">
-        <v>75.47</v>
+        <v>103.97</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="P6" t="n">
-        <v>4.97</v>
+        <v>7.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.8099999999999999</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
@@ -1377,13 +1375,13 @@
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>0.09055399608071607</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NE002006</t>
+          <t>NE002005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -1392,64 +1390,64 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NE002004</t>
+          <t>NE006004</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NE002004;NE002006;NE005013;NE006011</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>58.6</v>
+        <v>17.7</v>
       </c>
       <c r="I7" t="n">
-        <v>34.4</v>
+        <v>77.3</v>
       </c>
       <c r="J7" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>41.4</v>
+        <v>82.3</v>
       </c>
       <c r="M7" t="n">
-        <v>148.77</v>
+        <v>75.47</v>
       </c>
       <c r="N7" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>11.35</v>
+        <v>4.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
@@ -1493,13 +1491,13 @@
       <c r="BL7" t="inlineStr"/>
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="n">
-        <v>0.4003178206583428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NE003001</t>
+          <t>NE002006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -1508,64 +1506,64 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NE005008</t>
+          <t>NE002004</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE002004;NE002006;NE005013;NE006011</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>41.6</v>
+        <v>58.6</v>
       </c>
       <c r="I8" t="n">
-        <v>57.4</v>
+        <v>34.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L8" t="n">
-        <v>58.4</v>
+        <v>41.4</v>
       </c>
       <c r="M8" t="n">
-        <v>56.84</v>
+        <v>148.77</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.720000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="T8" t="n">
-        <v>1.07</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
@@ -1609,13 +1607,13 @@
       <c r="BL8" t="inlineStr"/>
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>0.4003178206583428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NE003002</t>
+          <t>NE003001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -1624,31 +1622,31 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NE003003</t>
+          <t>NE005008</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NE003002;NE003003;NE003005</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>58.5</v>
+        <v>41.6</v>
       </c>
       <c r="I9" t="n">
-        <v>41.5</v>
+        <v>57.4</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>58.4</v>
       </c>
       <c r="M9" t="n">
-        <v>41.34</v>
+        <v>56.84</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1669,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1731,7 +1729,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NE003003</t>
+          <t>NE003002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -1740,7 +1738,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NE003005</t>
+          <t>NE003003</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1749,10 +1747,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>62.4</v>
+        <v>58.5</v>
       </c>
       <c r="I10" t="n">
-        <v>37.5</v>
+        <v>41.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1761,10 +1759,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>37.6</v>
+        <v>41.5</v>
       </c>
       <c r="M10" t="n">
-        <v>76.86</v>
+        <v>41.34</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1794,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1826,72 +1824,28 @@
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>Dosso</t>
-        </is>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>NE003</t>
-        </is>
-      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>Islamic State Sahel Province (ISSP)</t>
-        </is>
-      </c>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>Civilians (Niger)</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>Teachers (Niger)</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>On 17 March 2024, likely IS Sahel militants opened fire on a teacher near Dogondoutchi (Dogondoutchi, Dosso). The bullets did not hit the teacher who fled the area.</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>Dogondoutchi</t>
-        </is>
-      </c>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="n">
-        <v>0.002268536887063272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NE003004</t>
+          <t>NE003003</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1900,31 +1854,31 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NE003004</t>
+          <t>NE003005</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NE003004</t>
+          <t>NE003002;NE003003;NE003005</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>63.3</v>
+        <v>62.4</v>
       </c>
       <c r="I11" t="n">
-        <v>36.4</v>
+        <v>37.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>36.7</v>
+        <v>37.6</v>
       </c>
       <c r="M11" t="n">
-        <v>35.07</v>
+        <v>76.86</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1954,10 +1908,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="X11" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
@@ -1995,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
@@ -2005,53 +1959,53 @@
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>Riots ---- Protests</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>Violent demonstration ---- Peaceful protest</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Rioters (Niger) ---- Protesters (Niger)</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>Students (Niger) ---- SYNACEB: National Union of Contract Agents and Basic Education Officers; Teachers (Niger)</t>
-        </is>
-      </c>
+          <t>Islamic State Sahel Province (ISSP)</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Police Forces of Niger (2023-)</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr"/>
+          <t>Civilians (Niger)</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>Teachers (Niger)</t>
+        </is>
+      </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>On 14 October 2024, students clashed with police forces near the university in Dosso (Dosso, Dosso). The students were marching towards the governorate to demand a response to previous incidents involving security forces. Clashes erupted when security forces used tear gas to disperse the crowd. Students responded by throwing stones, erecting barricades, and setting fire to the main road in front of the campus. Casualties unknown. ---- On 24 March 2025, contractual teachers from the National Union of Contractual Agents and Civil Servants in Basic Education (SYNACEB) organized a sit-in in front of the governorate in Dosso (Dosso, Dosso) to denounce irregularities in the payment of their wages.</t>
+          <t>On 17 March 2024, likely IS Sahel militants opened fire on a teacher near Dogondoutchi (Dogondoutchi, Dosso). The bullets did not hit the teacher who fled the area.</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>2024-10-14 ---- 2025-03-24</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>Dosso</t>
+          <t>Dogondoutchi</t>
         </is>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>0.002268536887063272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NE003005</t>
+          <t>NE003004</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -2060,31 +2014,31 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NE003003</t>
+          <t>NE003004</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NE003002;NE003003;NE003005</t>
+          <t>NE003004</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>66.3</v>
+        <v>63.3</v>
       </c>
       <c r="I12" t="n">
-        <v>33.7</v>
+        <v>36.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L12" t="n">
-        <v>33.7</v>
+        <v>36.7</v>
       </c>
       <c r="M12" t="n">
-        <v>32.23</v>
+        <v>35.07</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2117,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
@@ -2146,20 +2100,64 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>Dosso</t>
+        </is>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>NE003</t>
+        </is>
+      </c>
       <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>Riots ---- Protests</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>Violent demonstration ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Rioters (Niger) ---- Protesters (Niger)</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>Students (Niger) ---- SYNACEB: National Union of Contract Agents and Basic Education Officers; Teachers (Niger)</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Police Forces of Niger (2023-)</t>
+        </is>
+      </c>
       <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>On 14 October 2024, students clashed with police forces near the university in Dosso (Dosso, Dosso). The students were marching towards the governorate to demand a response to previous incidents involving security forces. Clashes erupted when security forces used tear gas to disperse the crowd. Students responded by throwing stones, erecting barricades, and setting fire to the main road in front of the campus. Casualties unknown. ---- On 24 March 2025, contractual teachers from the National Union of Contractual Agents and Civil Servants in Basic Education (SYNACEB) organized a sit-in in front of the governorate in Dosso (Dosso, Dosso) to denounce irregularities in the payment of their wages.</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>2024-10-14 ---- 2025-03-24</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>Dosso</t>
+        </is>
+      </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
@@ -2167,7 +2165,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NE003006</t>
+          <t>NE003005</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -2176,40 +2174,40 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NE006009</t>
+          <t>NE003003</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
+          <t>NE003002;NE003003;NE003005</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>64</v>
+        <v>66.3</v>
       </c>
       <c r="I13" t="n">
-        <v>35.2</v>
+        <v>33.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>36</v>
+        <v>33.7</v>
       </c>
       <c r="M13" t="n">
-        <v>94.47</v>
+        <v>32.23</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2218,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -2277,13 +2275,13 @@
       <c r="BL13" t="inlineStr"/>
       <c r="BM13" t="inlineStr"/>
       <c r="BN13" t="n">
-        <v>0.00683120024454102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NE003007</t>
+          <t>NE003006</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -2292,49 +2290,49 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NE006001</t>
+          <t>NE006009</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>64.5</v>
+        <v>64</v>
       </c>
       <c r="I14" t="n">
-        <v>28.1</v>
+        <v>35.2</v>
       </c>
       <c r="J14" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="M14" t="n">
-        <v>26.85</v>
+        <v>94.47</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.31</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2346,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2378,72 +2376,28 @@
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>Dosso</t>
-        </is>
-      </c>
-      <c r="BA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>NE003</t>
-        </is>
-      </c>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>Islamic State Sahel Province (ISSP)</t>
-        </is>
-      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>Civilians (Niger)</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>Students (Niger)</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>On 13 April 2025, armed militants (likely affiliated with ISSP, based on location) raided the village of Kouro Beri (Loga, Dosso) and Adabaye (coded separately). During the extortion of zakat taxes, the militants killed 1 student in Kouro Beri.</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>Loga</t>
-        </is>
-      </c>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>0.00683120024454102</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NE003008</t>
+          <t>NE003007</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -2452,52 +2406,52 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NE005003</t>
+          <t>NE006001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>60.4</v>
+        <v>64.5</v>
       </c>
       <c r="I15" t="n">
-        <v>38.8</v>
+        <v>28.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>7.4</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>39.6</v>
+        <v>35.5</v>
       </c>
       <c r="M15" t="n">
-        <v>37.59</v>
+        <v>26.85</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="T15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2506,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2538,20 +2492,64 @@
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>Dosso</t>
+        </is>
+      </c>
+      <c r="BA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>NE003</t>
+        </is>
+      </c>
       <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Islamic State Sahel Province (ISSP)</t>
+        </is>
+      </c>
       <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="inlineStr"/>
-      <c r="BM15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Civilians (Niger)</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>Students (Niger)</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>On 13 April 2025, armed militants (likely affiliated with ISSP, based on location) raided the village of Kouro Beri (Loga, Dosso) and Adabaye (coded separately). During the extortion of zakat taxes, the militants killed 1 student in Kouro Beri.</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>Loga</t>
+        </is>
+      </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
@@ -2559,7 +2557,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NE004001</t>
+          <t>NE003008</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -2568,52 +2566,52 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NE002003</t>
+          <t>NE005003</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>42.8</v>
+        <v>60.4</v>
       </c>
       <c r="I16" t="n">
-        <v>42.8</v>
+        <v>38.8</v>
       </c>
       <c r="J16" t="n">
-        <v>13.8</v>
+        <v>0.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>57.2</v>
+        <v>39.6</v>
       </c>
       <c r="M16" t="n">
-        <v>42.29</v>
+        <v>37.59</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6</v>
+        <v>0.25</v>
       </c>
       <c r="P16" t="n">
-        <v>6.12</v>
+        <v>0.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2625,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
@@ -2675,7 +2673,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NE004002</t>
+          <t>NE004001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -2684,7 +2682,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NE004006</t>
+          <t>NE002003</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2693,40 +2691,40 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>40.1</v>
+        <v>42.8</v>
       </c>
       <c r="I17" t="n">
-        <v>53.8</v>
+        <v>42.8</v>
       </c>
       <c r="J17" t="n">
-        <v>5.7</v>
+        <v>13.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L17" t="n">
-        <v>59.9</v>
+        <v>57.2</v>
       </c>
       <c r="M17" t="n">
-        <v>42.65</v>
+        <v>42.29</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.72</v>
+        <v>1.6</v>
       </c>
       <c r="P17" t="n">
-        <v>5.02</v>
+        <v>6.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -2741,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
@@ -2791,7 +2789,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NE004003</t>
+          <t>NE004002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -2800,52 +2798,52 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NE005007</t>
+          <t>NE004006</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>35.1</v>
+        <v>40.1</v>
       </c>
       <c r="I18" t="n">
-        <v>61.1</v>
+        <v>53.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L18" t="n">
-        <v>64.90000000000001</v>
+        <v>59.9</v>
       </c>
       <c r="M18" t="n">
-        <v>60.53</v>
+        <v>42.65</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>5.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2857,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
@@ -2907,7 +2905,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NE004004</t>
+          <t>NE004003</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -2916,7 +2914,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NE005005</t>
+          <t>NE005007</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2925,43 +2923,43 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>52.2</v>
+        <v>35.1</v>
       </c>
       <c r="I19" t="n">
-        <v>45.8</v>
+        <v>61.1</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>47.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>44.83</v>
+        <v>60.53</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="S19" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -3023,7 +3021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NE004005</t>
+          <t>NE004004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -3032,52 +3030,52 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NE005003</t>
+          <t>NE005005</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>53.1</v>
+        <v>52.2</v>
       </c>
       <c r="I20" t="n">
-        <v>43.6</v>
+        <v>45.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>46.9</v>
+        <v>47.8</v>
       </c>
       <c r="M20" t="n">
-        <v>204.88</v>
+        <v>44.83</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.22</v>
+        <v>1.72</v>
       </c>
       <c r="P20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.82</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>17.24</v>
+        <v>0.25</v>
       </c>
       <c r="T20" t="n">
-        <v>13.05</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -3133,13 +3131,13 @@
       <c r="BL20" t="inlineStr"/>
       <c r="BM20" t="inlineStr"/>
       <c r="BN20" t="n">
-        <v>0.01211911571222968</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NE004006</t>
+          <t>NE004005</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -3148,64 +3146,64 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NE004002</t>
+          <t>NE005003</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>63.8</v>
+        <v>53.1</v>
       </c>
       <c r="I21" t="n">
-        <v>31.5</v>
+        <v>43.6</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>36.2</v>
+        <v>46.9</v>
       </c>
       <c r="M21" t="n">
-        <v>118.35</v>
+        <v>204.88</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.48</v>
+        <v>0.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.23</v>
+        <v>1.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.33</v>
+        <v>16.82</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S21" t="n">
-        <v>14.53</v>
+        <v>17.24</v>
       </c>
       <c r="T21" t="n">
-        <v>4.72</v>
+        <v>13.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
@@ -3249,13 +3247,13 @@
       <c r="BL21" t="inlineStr"/>
       <c r="BM21" t="inlineStr"/>
       <c r="BN21" t="n">
-        <v>0.01035549276413762</v>
+        <v>0.01211911571222968</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NE004007</t>
+          <t>NE004006</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -3264,64 +3262,64 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NE005007</t>
+          <t>NE004002</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>78.7</v>
+        <v>63.8</v>
       </c>
       <c r="I22" t="n">
-        <v>19.4</v>
+        <v>31.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L22" t="n">
-        <v>21.3</v>
+        <v>36.2</v>
       </c>
       <c r="M22" t="n">
-        <v>19.01</v>
+        <v>118.35</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.41</v>
+        <v>1.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0.41</v>
+        <v>2.23</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.03</v>
+        <v>2.33</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>14.53</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
@@ -3350,68 +3348,28 @@
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>Maradi</t>
-        </is>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>NE004</t>
-        </is>
-      </c>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
       <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>Protests ---- Protests</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>Peaceful protest ---- Peaceful protest</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>Protesters (Niger) ---- Protesters (Niger)</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>Muslim Group (Niger) ---- Students (Niger); USN: Union of Nigerien Students</t>
-        </is>
-      </c>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr"/>
       <c r="BJ22" t="inlineStr"/>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>On 5 April 2024, many residents carrying Palestinian flags demonstrated in support for Palestine in Maradi (Ville de Maradi, Maradi). The protest was organized by a few Koranic schools of Shiite obedience. ---- On 29 April 2024, thousands of students including members of the USN staged a demonstration in Maradi (Ville de Maradi, Maradi) in support of the National Council for the Safeguarding of the Homeland (CNSP) decision to expel all foreign forces from Niger.</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>2024-04-05 ---- 2024-04-29</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>Ville de Maradi</t>
-        </is>
-      </c>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>0.01035549276413762</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NE004008</t>
+          <t>NE004007</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -3420,7 +3378,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NE005008</t>
+          <t>NE005007</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3429,34 +3387,34 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>54.6</v>
+        <v>78.7</v>
       </c>
       <c r="I23" t="n">
-        <v>44.2</v>
+        <v>19.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>45.4</v>
+        <v>21.3</v>
       </c>
       <c r="M23" t="n">
-        <v>43.65</v>
+        <v>19.01</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.27</v>
+        <v>0.41</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3506,20 +3464,60 @@
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="inlineStr"/>
-      <c r="BB23" t="inlineStr"/>
-      <c r="BC23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>Maradi</t>
+        </is>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>NE004</t>
+        </is>
+      </c>
       <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="inlineStr"/>
-      <c r="BF23" t="inlineStr"/>
-      <c r="BG23" t="inlineStr"/>
-      <c r="BH23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>Protesters (Niger) ---- Protesters (Niger)</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>Muslim Group (Niger) ---- Students (Niger); USN: Union of Nigerien Students</t>
+        </is>
+      </c>
       <c r="BI23" t="inlineStr"/>
       <c r="BJ23" t="inlineStr"/>
-      <c r="BK23" t="inlineStr"/>
-      <c r="BL23" t="inlineStr"/>
-      <c r="BM23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>On 5 April 2024, many residents carrying Palestinian flags demonstrated in support for Palestine in Maradi (Ville de Maradi, Maradi). The protest was organized by a few Koranic schools of Shiite obedience. ---- On 29 April 2024, thousands of students including members of the USN staged a demonstration in Maradi (Ville de Maradi, Maradi) in support of the National Council for the Safeguarding of the Homeland (CNSP) decision to expel all foreign forces from Niger.</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>2024-04-05 ---- 2024-04-29</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>Ville de Maradi</t>
+        </is>
+      </c>
       <c r="BN23" t="n">
         <v>0</v>
       </c>
@@ -3527,7 +3525,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NE004009</t>
+          <t>NE004008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -3536,43 +3534,43 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NE006012</t>
+          <t>NE005008</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>36</v>
+        <v>54.6</v>
       </c>
       <c r="I24" t="n">
-        <v>60.8</v>
+        <v>44.2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>64</v>
+        <v>45.4</v>
       </c>
       <c r="M24" t="n">
-        <v>56.8</v>
+        <v>43.65</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3581,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3643,7 +3641,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NE005001</t>
+          <t>NE004009</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -3652,7 +3650,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NE004005</t>
+          <t>NE006012</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3661,34 +3659,34 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>51.2</v>
+        <v>36</v>
       </c>
       <c r="I25" t="n">
-        <v>41.6</v>
+        <v>60.8</v>
       </c>
       <c r="J25" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>48.8</v>
+        <v>64</v>
       </c>
       <c r="M25" t="n">
-        <v>40.1</v>
+        <v>56.8</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.51</v>
+        <v>1.33</v>
       </c>
       <c r="P25" t="n">
-        <v>3.08</v>
+        <v>0.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3697,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3706,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -3759,7 +3757,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NE005002</t>
+          <t>NE005001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -3768,49 +3766,49 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NE005007</t>
+          <t>NE004005</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>61</v>
+        <v>51.2</v>
       </c>
       <c r="I26" t="n">
-        <v>35.4</v>
+        <v>41.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>39</v>
+        <v>48.8</v>
       </c>
       <c r="M26" t="n">
-        <v>78.14</v>
+        <v>40.1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.06</v>
+        <v>0.51</v>
       </c>
       <c r="P26" t="n">
-        <v>3.37</v>
+        <v>3.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -3822,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -3869,13 +3867,13 @@
       <c r="BL26" t="inlineStr"/>
       <c r="BM26" t="inlineStr"/>
       <c r="BN26" t="n">
-        <v>0.05348192126137525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NE005003</t>
+          <t>NE005002</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -3884,58 +3882,58 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NE004005</t>
+          <t>NE005007</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>53.1</v>
+        <v>61</v>
       </c>
       <c r="I27" t="n">
-        <v>45.1</v>
+        <v>35.4</v>
       </c>
       <c r="J27" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>46.9</v>
+        <v>39</v>
       </c>
       <c r="M27" t="n">
-        <v>43.5</v>
+        <v>78.14</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0.27</v>
+        <v>3.06</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8</v>
+        <v>3.37</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -3985,13 +3983,13 @@
       <c r="BL27" t="inlineStr"/>
       <c r="BM27" t="inlineStr"/>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>0.05348192126137525</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NE005004</t>
+          <t>NE005003</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -4000,19 +3998,19 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NE002005</t>
+          <t>NE004005</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>47.3</v>
+        <v>53.1</v>
       </c>
       <c r="I28" t="n">
-        <v>50.8</v>
+        <v>45.1</v>
       </c>
       <c r="J28" t="n">
         <v>1.9</v>
@@ -4021,37 +4019,37 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>52.7</v>
+        <v>46.9</v>
       </c>
       <c r="M28" t="n">
-        <v>45.45</v>
+        <v>43.5</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.6</v>
+        <v>0.27</v>
       </c>
       <c r="P28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V28" t="n">
         <v>0.27</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -4107,7 +4105,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NE005005</t>
+          <t>NE005004</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -4116,7 +4114,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NE004004</t>
+          <t>NE002005</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4125,31 +4123,31 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>55.5</v>
+        <v>47.3</v>
       </c>
       <c r="I29" t="n">
-        <v>42.5</v>
+        <v>50.8</v>
       </c>
       <c r="J29" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>44.5</v>
+        <v>52.7</v>
       </c>
       <c r="M29" t="n">
-        <v>40.75</v>
+        <v>45.45</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="P29" t="n">
-        <v>0.68</v>
+        <v>0.27</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -4223,7 +4221,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NE005006</t>
+          <t>NE005005</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -4232,7 +4230,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NE006004</t>
+          <t>NE004004</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4241,34 +4239,34 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>65.5</v>
+        <v>55.5</v>
       </c>
       <c r="I30" t="n">
-        <v>30.4</v>
+        <v>42.5</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>34.5</v>
+        <v>44.5</v>
       </c>
       <c r="M30" t="n">
-        <v>27.7</v>
+        <v>40.75</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.03</v>
+        <v>1.37</v>
       </c>
       <c r="P30" t="n">
-        <v>1.35</v>
+        <v>0.68</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4339,7 +4337,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NE005007</t>
+          <t>NE005006</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -4348,7 +4346,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NE004003</t>
+          <t>NE006004</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4357,55 +4355,55 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>45.7</v>
+        <v>65.5</v>
       </c>
       <c r="I31" t="n">
-        <v>49.5</v>
+        <v>30.4</v>
       </c>
       <c r="J31" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>54.3</v>
+        <v>34.5</v>
       </c>
       <c r="M31" t="n">
-        <v>191.11</v>
+        <v>27.7</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="P31" t="n">
-        <v>24.3</v>
+        <v>1.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>9.99</v>
+        <v>0.68</v>
       </c>
       <c r="R31" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>12.27</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.9400000000000001</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
@@ -4449,13 +4447,13 @@
       <c r="BL31" t="inlineStr"/>
       <c r="BM31" t="inlineStr"/>
       <c r="BN31" t="n">
-        <v>0.005652259671096427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NE005008</t>
+          <t>NE005007</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -4464,7 +4462,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NE003001</t>
+          <t>NE004003</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4473,55 +4471,55 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>46.6</v>
+        <v>45.7</v>
       </c>
       <c r="I32" t="n">
-        <v>52.4</v>
+        <v>49.5</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>53.4</v>
+        <v>54.3</v>
       </c>
       <c r="M32" t="n">
-        <v>51.93</v>
+        <v>191.11</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0.72</v>
+        <v>1.98</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.24</v>
+        <v>9.99</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>12.27</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
@@ -4565,13 +4563,13 @@
       <c r="BL32" t="inlineStr"/>
       <c r="BM32" t="inlineStr"/>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>0.005652259671096427</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NE005009</t>
+          <t>NE005008</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -4580,43 +4578,43 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NE006002</t>
+          <t>NE003001</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>52.9</v>
+        <v>46.6</v>
       </c>
       <c r="I33" t="n">
-        <v>42.6</v>
+        <v>52.4</v>
       </c>
       <c r="J33" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>47.1</v>
+        <v>53.4</v>
       </c>
       <c r="M33" t="n">
-        <v>94.21000000000001</v>
+        <v>51.93</v>
       </c>
       <c r="N33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.04</v>
+        <v>0.72</v>
       </c>
       <c r="P33" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.6</v>
+        <v>0.24</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4625,112 +4623,46 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
-      <c r="Y33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>2024-02-04</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>February 2024: students were removed from their classes at a school by suspected IS Sahel militants.</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>Islamic State</t>
-        </is>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="AV33" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
       <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+      <c r="AX33" t="inlineStr"/>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="inlineStr"/>
@@ -4747,13 +4679,13 @@
       <c r="BL33" t="inlineStr"/>
       <c r="BM33" t="inlineStr"/>
       <c r="BN33" t="n">
-        <v>0.00642803895929316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NE005010</t>
+          <t>NE005009</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -4762,91 +4694,157 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NE006010</t>
+          <t>NE006002</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>35.7</v>
+        <v>52.9</v>
       </c>
       <c r="I34" t="n">
-        <v>45.6</v>
+        <v>42.6</v>
       </c>
       <c r="J34" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>64.3</v>
+        <v>47.1</v>
       </c>
       <c r="M34" t="n">
-        <v>86.97</v>
+        <v>94.21000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O34" t="n">
-        <v>3.98</v>
+        <v>3.04</v>
       </c>
       <c r="P34" t="n">
-        <v>13.84</v>
+        <v>2.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.31</v>
+        <v>0.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0.89</v>
+        <v>0.35</v>
       </c>
       <c r="U34" t="n">
-        <v>3.31</v>
+        <v>1.06</v>
       </c>
       <c r="V34" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>2024-02-04</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>February 2024: students were removed from their classes at a school by suspected IS Sahel militants.</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>Islamic State</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
       <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="inlineStr"/>
@@ -4863,13 +4861,13 @@
       <c r="BL34" t="inlineStr"/>
       <c r="BM34" t="inlineStr"/>
       <c r="BN34" t="n">
-        <v>0.5016542002301496</v>
+        <v>0.00642803895929316</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NE005011</t>
+          <t>NE005010</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -4878,61 +4876,61 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NE006009</t>
+          <t>NE006010</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>28.4</v>
+        <v>35.7</v>
       </c>
       <c r="I35" t="n">
-        <v>70.09999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="J35" t="n">
-        <v>1.5</v>
+        <v>18.7</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>71.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="M35" t="n">
-        <v>167.92</v>
+        <v>86.97</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P35" t="n">
-        <v>1.23</v>
+        <v>13.84</v>
       </c>
       <c r="Q35" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.31</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -4979,13 +4977,13 @@
       <c r="BL35" t="inlineStr"/>
       <c r="BM35" t="inlineStr"/>
       <c r="BN35" t="n">
-        <v>0.01920465567410281</v>
+        <v>0.5016542002301496</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NE005012</t>
+          <t>NE005011</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -4994,7 +4992,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NE006007</t>
+          <t>NE006009</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5003,52 +5001,52 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>38.3</v>
+        <v>28.4</v>
       </c>
       <c r="I36" t="n">
-        <v>20.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>41.2</v>
+        <v>1.5</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>61.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>64.24000000000001</v>
+        <v>167.92</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>14.38</v>
+        <v>1.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.12</v>
+        <v>0.31</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>66.77</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>13.69</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -5080,72 +5078,28 @@
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr"/>
       <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>Tahoua</t>
-        </is>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC36" t="inlineStr">
-        <is>
-          <t>NE005</t>
-        </is>
-      </c>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
       <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr">
-        <is>
-          <t>Strategic developments</t>
-        </is>
-      </c>
-      <c r="BF36" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr">
-        <is>
-          <t>Islamic State Sahel Province (ISSP)</t>
-        </is>
-      </c>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
-      <c r="BI36" t="inlineStr">
-        <is>
-          <t>Civilians (Niger)</t>
-        </is>
-      </c>
-      <c r="BJ36" t="inlineStr">
-        <is>
-          <t>Students (Niger)</t>
-        </is>
-      </c>
-      <c r="BK36" t="inlineStr">
-        <is>
-          <t>Non-violent activity: On 4 February 2024, likely IS Sahel militants removed students from their classes at a school in the village of Garin Ali (Tillia, Tahoua).</t>
-        </is>
-      </c>
-      <c r="BL36" t="inlineStr">
-        <is>
-          <t>2024-02-04</t>
-        </is>
-      </c>
-      <c r="BM36" t="inlineStr">
-        <is>
-          <t>Tillia</t>
-        </is>
-      </c>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
       <c r="BN36" t="n">
-        <v>0.2978905359179019</v>
+        <v>0.01920465567410281</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NE005013</t>
+          <t>NE005012</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -5154,64 +5108,64 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NE006011</t>
+          <t>NE006007</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NE002004;NE002006;NE005013;NE006011</t>
+          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
         </is>
       </c>
       <c r="H37" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>61.7</v>
       </c>
-      <c r="I37" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="J37" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L37" t="n">
-        <v>38.3</v>
-      </c>
       <c r="M37" t="n">
-        <v>67.16</v>
+        <v>64.24000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.65</v>
+        <v>0.8</v>
       </c>
       <c r="P37" t="n">
-        <v>5.15</v>
+        <v>14.38</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.93</v>
+        <v>1.12</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>5.12</v>
+        <v>66.77</v>
       </c>
       <c r="T37" t="n">
-        <v>0.93</v>
+        <v>0.4</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>13.69</v>
       </c>
       <c r="X37" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
@@ -5249,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
@@ -5259,49 +5213,53 @@
       <c r="BD37" t="inlineStr"/>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>Protests ---- Protests</t>
+          <t>Strategic developments</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Peaceful protest</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>Protesters (Niger) ---- Protesters (Niger)</t>
-        </is>
-      </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>Students (Niger); USN: Union of Nigerien Students ---- ITN: Inter-union of Workers of Niger; Labor Group (Niger); SNEB: National Union of the Teachers of Basic education; Teachers (Niger)</t>
-        </is>
-      </c>
-      <c r="BI37" t="inlineStr"/>
-      <c r="BJ37" t="inlineStr"/>
+          <t>Islamic State Sahel Province (ISSP)</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>Civilians (Niger)</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>Students (Niger)</t>
+        </is>
+      </c>
       <c r="BK37" t="inlineStr">
         <is>
-          <t>On 29 April 2024, thousands of students including members of the USN staged a demonstration in Tahoua (Ville de Tahoua, Tahoua). The protesters demanded the revision of all mining and oil agreements and the closure of all foreign bases in Niger. ---- On 1 May 2025, at the call of unions (ITN, SNEB), workers demonstrated in Tahoua (Ville de Tahoua, Tahoua) to commemorate International Workers' Day. They called for the improvement of the working and living conditions for Niger's workers.</t>
+          <t>Non-violent activity: On 4 February 2024, likely IS Sahel militants removed students from their classes at a school in the village of Garin Ali (Tillia, Tahoua).</t>
         </is>
       </c>
       <c r="BL37" t="inlineStr">
         <is>
-          <t>2024-04-29 ---- 2025-05-01</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="BM37" t="inlineStr">
         <is>
-          <t>Ville de Tahoua</t>
+          <t>Tillia</t>
         </is>
       </c>
       <c r="BN37" t="n">
-        <v>0</v>
+        <v>0.2978905359179019</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NE006001</t>
+          <t>NE005013</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -5310,52 +5268,52 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NE003007</t>
+          <t>NE006011</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE002004;NE002006;NE005013;NE006011</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>63.2</v>
+        <v>61.7</v>
       </c>
       <c r="I38" t="n">
-        <v>29.4</v>
+        <v>31.5</v>
       </c>
       <c r="J38" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L38" t="n">
-        <v>36.8</v>
+        <v>38.3</v>
       </c>
       <c r="M38" t="n">
-        <v>94.65000000000001</v>
+        <v>67.16</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="O38" t="n">
-        <v>1.38</v>
+        <v>2.65</v>
       </c>
       <c r="P38" t="n">
-        <v>7.07</v>
+        <v>5.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.08</v>
+        <v>1.93</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.25</v>
+        <v>5.12</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5364,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
@@ -5398,70 +5356,66 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>Tillaberi</t>
+          <t>Tahoua</t>
         </is>
       </c>
       <c r="BA38" t="n">
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>NE006</t>
+          <t>NE005</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr"/>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>Strategic developments</t>
+          <t>Protests ---- Protests</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>Looting/property destruction</t>
+          <t>Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>Islamic State Sahel Province (ISSP)</t>
-        </is>
-      </c>
-      <c r="BH38" t="inlineStr"/>
-      <c r="BI38" t="inlineStr">
-        <is>
-          <t>Civilians (Niger)</t>
-        </is>
-      </c>
-      <c r="BJ38" t="inlineStr">
-        <is>
-          <t>Teachers (Niger)</t>
-        </is>
-      </c>
+          <t>Protesters (Niger) ---- Protesters (Niger)</t>
+        </is>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>Students (Niger); USN: Union of Nigerien Students ---- ITN: Inter-union of Workers of Niger; Labor Group (Niger); SNEB: National Union of the Teachers of Basic education; Teachers (Niger)</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
       <c r="BK38" t="inlineStr">
         <is>
-          <t>Looting: On 17 January 2024, likely IS Sahel militants extorted 'zakat' taxes from residents and seized cell phones and fuel from motorcycle tanks belonging to teachers in the village of Tapkin Kalgo (Filingue, Tillaberi).</t>
+          <t>On 29 April 2024, thousands of students including members of the USN staged a demonstration in Tahoua (Ville de Tahoua, Tahoua). The protesters demanded the revision of all mining and oil agreements and the closure of all foreign bases in Niger. ---- On 1 May 2025, at the call of unions (ITN, SNEB), workers demonstrated in Tahoua (Ville de Tahoua, Tahoua) to commemorate International Workers' Day. They called for the improvement of the working and living conditions for Niger's workers.</t>
         </is>
       </c>
       <c r="BL38" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-04-29 ---- 2025-05-01</t>
         </is>
       </c>
       <c r="BM38" t="inlineStr">
         <is>
-          <t>Abala</t>
+          <t>Ville de Tahoua</t>
         </is>
       </c>
       <c r="BN38" t="n">
-        <v>0.07642879415564167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NE006002</t>
+          <t>NE006001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -5470,49 +5424,49 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NE006005</t>
+          <t>NE003007</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>47.8</v>
+        <v>63.2</v>
       </c>
       <c r="I39" t="n">
-        <v>39.1</v>
+        <v>29.4</v>
       </c>
       <c r="J39" t="n">
-        <v>13.1</v>
+        <v>7.3</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>52.2</v>
+        <v>36.8</v>
       </c>
       <c r="M39" t="n">
-        <v>121.65</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="P39" t="n">
-        <v>0.67</v>
+        <v>7.07</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.91</v>
+        <v>3.08</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -5524,7 +5478,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>23.16</v>
+        <v>3.53</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5556,28 +5510,72 @@
       <c r="AW39" t="inlineStr"/>
       <c r="AX39" t="inlineStr"/>
       <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
-      <c r="BB39" t="inlineStr"/>
-      <c r="BC39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>Tillaberi</t>
+        </is>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
+      </c>
       <c r="BD39" t="inlineStr"/>
-      <c r="BE39" t="inlineStr"/>
-      <c r="BF39" t="inlineStr"/>
-      <c r="BG39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="BF39" t="inlineStr">
+        <is>
+          <t>Looting/property destruction</t>
+        </is>
+      </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>Islamic State Sahel Province (ISSP)</t>
+        </is>
+      </c>
       <c r="BH39" t="inlineStr"/>
-      <c r="BI39" t="inlineStr"/>
-      <c r="BJ39" t="inlineStr"/>
-      <c r="BK39" t="inlineStr"/>
-      <c r="BL39" t="inlineStr"/>
-      <c r="BM39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>Civilians (Niger)</t>
+        </is>
+      </c>
+      <c r="BJ39" t="inlineStr">
+        <is>
+          <t>Teachers (Niger)</t>
+        </is>
+      </c>
+      <c r="BK39" t="inlineStr">
+        <is>
+          <t>Looting: On 17 January 2024, likely IS Sahel militants extorted 'zakat' taxes from residents and seized cell phones and fuel from motorcycle tanks belonging to teachers in the village of Tapkin Kalgo (Filingue, Tillaberi).</t>
+        </is>
+      </c>
+      <c r="BL39" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="BM39" t="inlineStr">
+        <is>
+          <t>Abala</t>
+        </is>
+      </c>
       <c r="BN39" t="n">
-        <v>0.2286097636494994</v>
+        <v>0.07642879415564167</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NE006003</t>
+          <t>NE006002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -5586,43 +5584,43 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NE003001</t>
+          <t>NE006005</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>55.7</v>
+        <v>47.8</v>
       </c>
       <c r="I40" t="n">
-        <v>43.8</v>
+        <v>39.1</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5</v>
+        <v>13.1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>44.3</v>
+        <v>52.2</v>
       </c>
       <c r="M40" t="n">
-        <v>119.28</v>
+        <v>121.65</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.45</v>
+        <v>2.62</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5637,10 +5635,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>23.16</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -5687,13 +5685,13 @@
       <c r="BL40" t="inlineStr"/>
       <c r="BM40" t="inlineStr"/>
       <c r="BN40" t="n">
-        <v>0.01764771943334777</v>
+        <v>0.2286097636494994</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NE006004</t>
+          <t>NE006003</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -5702,7 +5700,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NE005006</t>
+          <t>NE003001</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5711,28 +5709,28 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>54.8</v>
+        <v>55.7</v>
       </c>
       <c r="I41" t="n">
-        <v>39.3</v>
+        <v>43.8</v>
       </c>
       <c r="J41" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>45.2</v>
+        <v>44.3</v>
       </c>
       <c r="M41" t="n">
-        <v>90.46000000000001</v>
+        <v>119.28</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -5747,16 +5745,16 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="W41" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -5803,13 +5801,13 @@
       <c r="BL41" t="inlineStr"/>
       <c r="BM41" t="inlineStr"/>
       <c r="BN41" t="n">
-        <v>0.1041051577623168</v>
+        <v>0.01764771943334777</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NE006005</t>
+          <t>NE006004</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -5818,40 +5816,40 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NE006002</t>
+          <t>NE005006</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>41.8</v>
+        <v>54.8</v>
       </c>
       <c r="I42" t="n">
-        <v>24.5</v>
+        <v>39.3</v>
       </c>
       <c r="J42" t="n">
-        <v>33.7</v>
+        <v>5.8</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>58.2</v>
+        <v>45.2</v>
       </c>
       <c r="M42" t="n">
-        <v>70.52</v>
+        <v>90.46000000000001</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -5860,19 +5858,19 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="U42" t="n">
-        <v>1.04</v>
+        <v>0.27</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>33.69</v>
+        <v>6.13</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -5919,13 +5917,13 @@
       <c r="BL42" t="inlineStr"/>
       <c r="BM42" t="inlineStr"/>
       <c r="BN42" t="n">
-        <v>0.02472110303496589</v>
+        <v>0.1041051577623168</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NE006006</t>
+          <t>NE006005</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -5934,64 +5932,64 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NE006001</t>
+          <t>NE006002</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>48.5</v>
+        <v>41.8</v>
       </c>
       <c r="I43" t="n">
-        <v>45</v>
+        <v>24.5</v>
       </c>
       <c r="J43" t="n">
-        <v>6.5</v>
+        <v>33.7</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>51.5</v>
+        <v>58.2</v>
       </c>
       <c r="M43" t="n">
-        <v>78.00999999999999</v>
+        <v>70.52</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1.15</v>
+        <v>1.92</v>
       </c>
       <c r="P43" t="n">
-        <v>11.33</v>
+        <v>1.31</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>10.27</v>
+        <v>0.35</v>
       </c>
       <c r="T43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>33.69</v>
       </c>
       <c r="X43" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
@@ -6035,13 +6033,13 @@
       <c r="BL43" t="inlineStr"/>
       <c r="BM43" t="inlineStr"/>
       <c r="BN43" t="n">
-        <v>0.0187722395001541</v>
+        <v>0.02472110303496589</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NE006007</t>
+          <t>NE006006</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -6050,64 +6048,64 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>NE005012</t>
+          <t>NE006001</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>37.1</v>
+        <v>48.5</v>
       </c>
       <c r="I44" t="n">
-        <v>47.8</v>
+        <v>45</v>
       </c>
       <c r="J44" t="n">
-        <v>15.1</v>
+        <v>6.5</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>62.9</v>
+        <v>51.5</v>
       </c>
       <c r="M44" t="n">
-        <v>121.08</v>
+        <v>78.00999999999999</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P44" t="n">
-        <v>4.95</v>
+        <v>11.33</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.31</v>
+        <v>3.49</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.78</v>
+        <v>10.27</v>
       </c>
       <c r="T44" t="n">
-        <v>0.98</v>
+        <v>3.15</v>
       </c>
       <c r="U44" t="n">
-        <v>1.73</v>
+        <v>0.91</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>11.87</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
@@ -6136,72 +6134,28 @@
       <c r="AW44" t="inlineStr"/>
       <c r="AX44" t="inlineStr"/>
       <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>Tillaberi</t>
-        </is>
-      </c>
-      <c r="BA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC44" t="inlineStr">
-        <is>
-          <t>NE006</t>
-        </is>
-      </c>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="inlineStr"/>
-      <c r="BE44" t="inlineStr">
-        <is>
-          <t>Strategic developments ---- Strategic developments ---- Strategic developments</t>
-        </is>
-      </c>
-      <c r="BF44" t="inlineStr">
-        <is>
-          <t>Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr">
-        <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
-        </is>
-      </c>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
       <c r="BH44" t="inlineStr"/>
-      <c r="BI44" t="inlineStr">
-        <is>
-          <t>Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger)</t>
-        </is>
-      </c>
-      <c r="BJ44" t="inlineStr">
-        <is>
-          <t>Students (Niger) ---- Students (Niger) ---- Students (Niger)</t>
-        </is>
-      </c>
-      <c r="BK44" t="inlineStr">
-        <is>
-          <t>Property destruction: On 15 April 2024, JNIM militants set some classrooms of a primary school on fire in the village of Dina (Gotheye, Tillaberi) during an incursion. Before withdrawing, the militants stole food from the school canteen. ---- Property destruction: On 25 April 2024, likely JNIM militants set classrooms of a school on fire in the village of Bangou Tara (Gotheye, Tillaberi). There were no casualties but several school equipment were destroyed. Alerted, an FDS unit managed to control the fire and launch an unsuccessful pursuit. ---- Property destruction: On 25 April 2024, JNIM fighters burned classrooms of a primary school during an incursion in the village of Bangou Karey Koulbaga (Gotheye, Tillaberi).</t>
-        </is>
-      </c>
-      <c r="BL44" t="inlineStr">
-        <is>
-          <t>2024-04-15 ---- 2024-04-25 ---- 2024-04-25</t>
-        </is>
-      </c>
-      <c r="BM44" t="inlineStr">
-        <is>
-          <t>Gotheye</t>
-        </is>
-      </c>
+      <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="inlineStr"/>
       <c r="BN44" t="n">
-        <v>0.05534044965452328</v>
+        <v>0.0187722395001541</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NE006008</t>
+          <t>NE006007</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -6210,31 +6164,31 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NE006008</t>
+          <t>NE005012</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NE006008</t>
+          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>64.90000000000001</v>
+        <v>37.1</v>
       </c>
       <c r="I45" t="n">
-        <v>35.1</v>
+        <v>47.8</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>15.1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>35.1</v>
+        <v>62.9</v>
       </c>
       <c r="M45" t="n">
-        <v>100.76</v>
+        <v>121.08</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6243,28 +6197,28 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.19</v>
+        <v>1.78</v>
       </c>
       <c r="T45" t="n">
-        <v>5.95</v>
+        <v>0.98</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>11.87</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -6296,28 +6250,72 @@
       <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="inlineStr"/>
       <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr"/>
-      <c r="BA45" t="inlineStr"/>
-      <c r="BB45" t="inlineStr"/>
-      <c r="BC45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>Tillaberi</t>
+        </is>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
+      </c>
       <c r="BD45" t="inlineStr"/>
-      <c r="BE45" t="inlineStr"/>
-      <c r="BF45" t="inlineStr"/>
-      <c r="BG45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Strategic developments ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction</t>
+        </is>
+      </c>
+      <c r="BG45" t="inlineStr">
+        <is>
+          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
+        </is>
+      </c>
       <c r="BH45" t="inlineStr"/>
-      <c r="BI45" t="inlineStr"/>
-      <c r="BJ45" t="inlineStr"/>
-      <c r="BK45" t="inlineStr"/>
-      <c r="BL45" t="inlineStr"/>
-      <c r="BM45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger)</t>
+        </is>
+      </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>Students (Niger) ---- Students (Niger) ---- Students (Niger)</t>
+        </is>
+      </c>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>Property destruction: On 15 April 2024, JNIM militants set some classrooms of a primary school on fire in the village of Dina (Gotheye, Tillaberi) during an incursion. Before withdrawing, the militants stole food from the school canteen. ---- Property destruction: On 25 April 2024, likely JNIM militants set classrooms of a school on fire in the village of Bangou Tara (Gotheye, Tillaberi). There were no casualties but several school equipment were destroyed. Alerted, an FDS unit managed to control the fire and launch an unsuccessful pursuit. ---- Property destruction: On 25 April 2024, JNIM fighters burned classrooms of a primary school during an incursion in the village of Bangou Karey Koulbaga (Gotheye, Tillaberi).</t>
+        </is>
+      </c>
+      <c r="BL45" t="inlineStr">
+        <is>
+          <t>2024-04-15 ---- 2024-04-25 ---- 2024-04-25</t>
+        </is>
+      </c>
+      <c r="BM45" t="inlineStr">
+        <is>
+          <t>Gotheye</t>
+        </is>
+      </c>
       <c r="BN45" t="n">
-        <v>0.0004394825185672131</v>
+        <v>0.05534044965452328</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NE006009</t>
+          <t>NE006008</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -6326,31 +6324,31 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NE005011</t>
+          <t>NE006008</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
+          <t>NE006008</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>78.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>20.5</v>
+        <v>35.1</v>
       </c>
       <c r="J46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>21.8</v>
+        <v>35.1</v>
       </c>
       <c r="M46" t="n">
-        <v>35.45</v>
+        <v>100.76</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6359,19 +6357,19 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.54</v>
+        <v>1.19</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -6380,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -6412,72 +6410,28 @@
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr"/>
       <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>Tillaberi</t>
-        </is>
-      </c>
-      <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC46" t="inlineStr">
-        <is>
-          <t>NE006</t>
-        </is>
-      </c>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
       <c r="BD46" t="inlineStr"/>
-      <c r="BE46" t="inlineStr">
-        <is>
-          <t>Strategic developments</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>Looting/property destruction</t>
-        </is>
-      </c>
-      <c r="BG46" t="inlineStr">
-        <is>
-          <t>Islamic State Sahel Province (ISSP)</t>
-        </is>
-      </c>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
-      <c r="BI46" t="inlineStr">
-        <is>
-          <t>Civilians (Niger)</t>
-        </is>
-      </c>
-      <c r="BJ46" t="inlineStr">
-        <is>
-          <t>Students (Niger)</t>
-        </is>
-      </c>
-      <c r="BK46" t="inlineStr">
-        <is>
-          <t>Property destruction: On 19 April 2024, likely IS Sahel militants set 4 houses and 4 sheds on fire after an incursion in the village of Samari Koira (Ouallam, Tillaberi).</t>
-        </is>
-      </c>
-      <c r="BL46" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="BM46" t="inlineStr">
-        <is>
-          <t>Ouallam</t>
-        </is>
-      </c>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
       <c r="BN46" t="n">
-        <v>0.01943990737486303</v>
+        <v>0.0004394825185672131</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NE006010</t>
+          <t>NE006009</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -6486,31 +6440,31 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NE005010</t>
+          <t>NE005011</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
+          <t>NE003006;NE005011;NE005012;NE006007;NE006009</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>45.9</v>
+        <v>78.2</v>
       </c>
       <c r="I47" t="n">
-        <v>34.7</v>
+        <v>20.5</v>
       </c>
       <c r="J47" t="n">
-        <v>19.4</v>
+        <v>1.3</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>54.1</v>
+        <v>21.8</v>
       </c>
       <c r="M47" t="n">
-        <v>69.97</v>
+        <v>35.45</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -6519,28 +6473,28 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>4.97</v>
+        <v>0.54</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>73.52</v>
+        <v>0.43</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -6581,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
@@ -6591,53 +6545,53 @@
       <c r="BD47" t="inlineStr"/>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments</t>
+          <t>Strategic developments</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction</t>
+          <t>Looting/property destruction</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
+          <t>Islamic State Sahel Province (ISSP)</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr"/>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger)</t>
+          <t>Civilians (Niger)</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
         <is>
-          <t>Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger)</t>
+          <t>Students (Niger)</t>
         </is>
       </c>
       <c r="BK47" t="inlineStr">
         <is>
-          <t>Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of Loudia Banda (Say, Tillaberi), Dokimana, Dyongore and 'Seckere' (coded separately). ---- Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of Dokimana (Say, Tillaberi), Loudia Banda, Dyongore and 'Seckere' (coded separately). ---- Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of Dyongore (Say, Tillaberi), Dokimana, Loudia Banda and 'Seckere' (coded separately). ---- Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of 'Seckere', in the area of Say (Say, Tillaberi), Loudia Banda, Dokimana and Dyongore (coded separately).</t>
+          <t>Property destruction: On 19 April 2024, likely IS Sahel militants set 4 houses and 4 sheds on fire after an incursion in the village of Samari Koira (Ouallam, Tillaberi).</t>
         </is>
       </c>
       <c r="BL47" t="inlineStr">
         <is>
-          <t>2024-12-18 ---- 2024-12-18 ---- 2024-12-18 ---- 2024-12-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="BM47" t="inlineStr">
         <is>
-          <t>Say</t>
+          <t>Ouallam</t>
         </is>
       </c>
       <c r="BN47" t="n">
-        <v>0.03474261107848894</v>
+        <v>0.01943990737486303</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NE006011</t>
+          <t>NE006010</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -6646,31 +6600,31 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NE005013</t>
+          <t>NE005010</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>NE002004;NE002006;NE005013;NE006011</t>
+          <t>NE002005;NE003001;NE003007;NE004003;NE004004;NE004007;NE004008;NE005002;NE005004;NE005005;NE005006;NE005007;NE005008;NE005010;NE006001;NE006003;NE006004;NE006006;NE006010</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>46.7</v>
+        <v>45.9</v>
       </c>
       <c r="I48" t="n">
-        <v>31.2</v>
+        <v>34.7</v>
       </c>
       <c r="J48" t="n">
-        <v>21.8</v>
+        <v>19.4</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>53.3</v>
+        <v>54.1</v>
       </c>
       <c r="M48" t="n">
-        <v>66.77</v>
+        <v>69.97</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -6679,31 +6633,31 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.36</v>
+        <v>4.97</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>22.93</v>
+        <v>73.52</v>
       </c>
       <c r="X48" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
@@ -6738,10 +6692,10 @@
         </is>
       </c>
       <c r="BA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
@@ -6751,49 +6705,53 @@
       <c r="BD48" t="inlineStr"/>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>Battles</t>
+          <t>Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>Armed clash</t>
+          <t>Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>Military Forces of Niger (2023-)</t>
+          <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>Islamic State Sahel Province (ISSP)</t>
-        </is>
-      </c>
-      <c r="BJ48" t="inlineStr"/>
+          <t>Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger)</t>
+        </is>
+      </c>
+      <c r="BJ48" t="inlineStr">
+        <is>
+          <t>Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger)</t>
+        </is>
+      </c>
       <c r="BK48" t="inlineStr">
         <is>
-          <t>Around 20 December 2024 (between 19 - 21 December), the Niger army killed an unidentified armed militant (likely ISSP based on location) and arrested 4 others in Dolbel (Tera, Tillaberi). The military then seized more than 500 millet sheaves previously hidden in a school by ISSP militants.</t>
+          <t>Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of Loudia Banda (Say, Tillaberi), Dokimana, Dyongore and 'Seckere' (coded separately). ---- Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of Dokimana (Say, Tillaberi), Loudia Banda, Dyongore and 'Seckere' (coded separately). ---- Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of Dyongore (Say, Tillaberi), Dokimana, Loudia Banda and 'Seckere' (coded separately). ---- Property destruction: Around 18 December 2024 (week of), JNIM burned down the schools of 'Seckere', in the area of Say (Say, Tillaberi), Loudia Banda, Dokimana and Dyongore (coded separately).</t>
         </is>
       </c>
       <c r="BL48" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-18 ---- 2024-12-18 ---- 2024-12-18 ---- 2024-12-18</t>
         </is>
       </c>
       <c r="BM48" t="inlineStr">
         <is>
-          <t>Tera</t>
+          <t>Say</t>
         </is>
       </c>
       <c r="BN48" t="n">
-        <v>0.06796245552329148</v>
+        <v>0.03474261107848894</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NE006012</t>
+          <t>NE006011</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -6802,31 +6760,31 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NE004009</t>
+          <t>NE005013</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
+          <t>NE002004;NE002006;NE005013;NE006011</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>69.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="I49" t="n">
-        <v>29</v>
+        <v>31.2</v>
       </c>
       <c r="J49" t="n">
-        <v>1.5</v>
+        <v>21.8</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L49" t="n">
-        <v>30.6</v>
+        <v>53.3</v>
       </c>
       <c r="M49" t="n">
-        <v>75.62</v>
+        <v>66.77</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -6835,31 +6793,31 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.6000000000000001</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.56</v>
+        <v>0.36</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>22.93</v>
       </c>
       <c r="X49" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
@@ -6894,7 +6852,7 @@
         </is>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB49" t="n">
         <v>1</v>
@@ -6907,49 +6865,49 @@
       <c r="BD49" t="inlineStr"/>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>Protests</t>
+          <t>Battles</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>Peaceful protest</t>
+          <t>Armed clash</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>Protesters (Niger)</t>
-        </is>
-      </c>
-      <c r="BH49" t="inlineStr">
-        <is>
-          <t>CDNT: Democratic Confederation of Workers of Niger; CGSL-NIGER: General Confederation of Free Trade Unions of Niger; CNT: Nigerien Confederation of Labour; Labor Group (Niger); SYNACEB: National Union of Contract Agents and Basic Education Officers; UDTN: Democratic Union of Workers of Niger; USTN: Union of Workers Unions of Niger</t>
-        </is>
-      </c>
-      <c r="BI49" t="inlineStr"/>
+          <t>Military Forces of Niger (2023-)</t>
+        </is>
+      </c>
+      <c r="BH49" t="inlineStr"/>
+      <c r="BI49" t="inlineStr">
+        <is>
+          <t>Islamic State Sahel Province (ISSP)</t>
+        </is>
+      </c>
       <c r="BJ49" t="inlineStr"/>
       <c r="BK49" t="inlineStr">
         <is>
-          <t>On 1 May 2025, at the call of unions (USTN, CGSL-NIGER, UDTN, CDNT, CNT and SYNACEB), workers demonstrated in Tillaberi (Tillaberi, Tillaberi) to commemorate International Workers' Day. They expressed support for the Government of Niger and the Military Forces of Niger and demanded clear answers to the workers' social demands.</t>
+          <t>Around 20 December 2024 (between 19 - 21 December), the Niger army killed an unidentified armed militant (likely ISSP based on location) and arrested 4 others in Dolbel (Tera, Tillaberi). The military then seized more than 500 millet sheaves previously hidden in a school by ISSP militants.</t>
         </is>
       </c>
       <c r="BL49" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="BM49" t="inlineStr">
         <is>
-          <t>Tillaberi</t>
+          <t>Tera</t>
         </is>
       </c>
       <c r="BN49" t="n">
-        <v>0.0665961065961066</v>
+        <v>0.06796245552329148</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NE006013</t>
+          <t>NE006012</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -6958,64 +6916,64 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NE002003</t>
+          <t>NE004009</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
+          <t>NE003008;NE004005;NE004009;NE005001;NE005003;NE005009;NE006002;NE006005;NE006012</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>45.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>29.7</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>24.7</v>
+        <v>1.5</v>
       </c>
       <c r="K50" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>54.8</v>
+        <v>30.6</v>
       </c>
       <c r="M50" t="n">
-        <v>61.79</v>
+        <v>75.62</v>
       </c>
       <c r="N50" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.65</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.3</v>
+        <v>2.56</v>
       </c>
       <c r="T50" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>34.37</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
@@ -7050,10 +7008,10 @@
         </is>
       </c>
       <c r="BA50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
@@ -7063,47 +7021,387 @@
       <c r="BD50" t="inlineStr"/>
       <c r="BE50" t="inlineStr">
         <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BF50" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>Protesters (Niger)</t>
+        </is>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>CDNT: Democratic Confederation of Workers of Niger; CGSL-NIGER: General Confederation of Free Trade Unions of Niger; CNT: Nigerien Confederation of Labour; Labor Group (Niger); SYNACEB: National Union of Contract Agents and Basic Education Officers; UDTN: Democratic Union of Workers of Niger; USTN: Union of Workers Unions of Niger</t>
+        </is>
+      </c>
+      <c r="BI50" t="inlineStr"/>
+      <c r="BJ50" t="inlineStr"/>
+      <c r="BK50" t="inlineStr">
+        <is>
+          <t>On 1 May 2025, at the call of unions (USTN, CGSL-NIGER, UDTN, CDNT, CNT and SYNACEB), workers demonstrated in Tillaberi (Tillaberi, Tillaberi) to commemorate International Workers' Day. They expressed support for the Government of Niger and the Military Forces of Niger and demanded clear answers to the workers' social demands.</t>
+        </is>
+      </c>
+      <c r="BL50" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="BM50" t="inlineStr">
+        <is>
+          <t>Tillaberi</t>
+        </is>
+      </c>
+      <c r="BN50" t="n">
+        <v>0.0665961065961066</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NE006013</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NE002003</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NE002001;NE002002;NE002003;NE004001;NE004002;NE004006;NE006013</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="J51" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="M51" t="n">
+        <v>61.79</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="W51" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>Tillaberi</t>
+        </is>
+      </c>
+      <c r="BA51" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>NE006</t>
+        </is>
+      </c>
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr">
+        <is>
           <t>Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Strategic developments ---- Violence against civilians</t>
         </is>
       </c>
-      <c r="BF50" t="inlineStr">
+      <c r="BF51" t="inlineStr">
         <is>
           <t>Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Looting/property destruction ---- Attack ---- Looting/property destruction ---- Attack</t>
         </is>
       </c>
-      <c r="BG50" t="inlineStr">
+      <c r="BG51" t="inlineStr">
         <is>
           <t>JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims ---- JNIM: Group for Support of Islam and Muslims</t>
         </is>
       </c>
-      <c r="BH50" t="inlineStr"/>
-      <c r="BI50" t="inlineStr">
+      <c r="BH51" t="inlineStr"/>
+      <c r="BI51" t="inlineStr">
         <is>
           <t>Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger) ---- Civilians (Niger)</t>
         </is>
       </c>
-      <c r="BJ50" t="inlineStr">
+      <c r="BJ51" t="inlineStr">
         <is>
           <t>Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Students (Niger); Teachers (Niger) ---- Teachers (Niger); Students (Niger) ---- Students (Niger); Teachers (Niger) ---- Muslim Group (Niger); Students (Niger); Teachers (Niger) ---- Labor Group (Niger) ---- Students (Niger); Teachers (Niger) ---- Teachers (Niger); SYNACEB: National Union of Contract Agents and Basic Education Officers</t>
         </is>
       </c>
-      <c r="BK50" t="inlineStr">
+      <c r="BK51" t="inlineStr">
         <is>
           <t>Property destruction: On 18 January 2025, overnight, armed militants (likely JNIM, based on location) burned down the school of 'Bogodjoti', a few kilometers north-west of Torodi, code to Kobio (Torodi, Tillaberi), a representative location in the area. ---- Property destruction: Around 20 January 2025 (between 19 - 22 January), an armed group (likely JNIM, based on the location) set fire to five classrooms in Djoga (Torodi, Tillaberi). They also fired shots in the air. ---- Property destruction: On 30 January 2025, JNIM militants burned down a school in the periphery of Torodi (Torodi, Tillaberi). ---- Property destruction: On 2 February 2025, JNIM militants burned down the school of Sirimbana (Torodi, Tillaberi). ---- Property destruction: On 11 February 2025, overnight, JNIM militants burned down the primary school of Tikko (Torodi, Tillaberi). ---- Property destruction: On 11 February 2025, overnight, JNIM militants burned down the primary school of 'Winde Silloube', coded to Kobadje (Torodi, Tillaberi), a representative center in the area. ---- Property destruction: On 11 February 2025, overnight, JNIM militants burned down the primary school, the middle school and the Quranic school of Kobadje (Torodi, Tillaberi). ---- On 1 May 2025, armed militants (likely JNIM, based on location) raided Makalondi (Makalondi, Torodi, Tillaberi), killing the president of the city's Schools Management Committee (COGES) and a trader. ---- Property destruction: On 16 May 2025, overnight, armed militants (likely JNIM, based on location) set fire to several schools of Kobadje (Torodi, Tillaberi). ---- On 13 June 2025, JNIM attacked a passenger vehicle between Makalondi and Torodi, coded to Niakatire (Torodi, Tillaberi), a middle point between the two locations, killing 9 civilians and injuring others. The National Union of Contract Agents and Basic Education Officers (SYNACEB) confirmed the death toll, adding that during the attack, SYNACEB members, a teacher of 'Banira' elementary school was killed and a teacher of Patti elementary school was seriously injured and evacuated to Niamey.</t>
         </is>
       </c>
-      <c r="BL50" t="inlineStr">
+      <c r="BL51" t="inlineStr">
         <is>
           <t>2025-01-18 ---- 2025-01-20 ---- 2025-01-30 ---- 2025-02-02 ---- 2025-02-11 ---- 2025-02-11 ---- 2025-02-11 ---- 2025-05-01 ---- 2025-05-16 ---- 2025-06-13</t>
         </is>
       </c>
-      <c r="BM50" t="inlineStr">
+      <c r="BM51" t="inlineStr">
         <is>
           <t>Torodi</t>
         </is>
       </c>
-      <c r="BN50" t="n">
+      <c r="BN51" t="n">
         <v>0.1575871091617567</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NE008001</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>April 2025: The rector of a university was stripped of their clothing when the university was invaded by members of the USN gang (Union of Nigerian Students) under the pretext that an order had not been respected. Educators were assaulted and a student was injured and had to be evacuated to a medical facility.</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>Civilian</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No Information on the Weapon Used</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>Niamey</t>
+        </is>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>NE008</t>
+        </is>
+      </c>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Violence against civilians ---- Protests ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Protests</t>
+        </is>
+      </c>
+      <c r="BF52" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Attack ---- Peaceful protest ---- Other ---- Other ---- Other ---- Attack ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BG52" t="inlineStr">
+        <is>
+          <t>Protesters (Niger) ---- Protesters (Niger) ---- Protesters (Niger) ---- Protesters (Niger) ---- Protesters (Niger) ---- CASO: Committee on Social Affairs and Order ---- Protesters (Niger) ---- Protesters (Niger) ---- Protesters (Niger) ---- Protesters (Niger) ---- CASO: Committee on Social Affairs and Order ---- Protesters (Niger)</t>
+        </is>
+      </c>
+      <c r="BH52" t="inlineStr">
+        <is>
+          <t>Students (Niger); USN: Union of Nigerien Students ---- Students (Niger); USN: Union of Nigerien Students ---- Students (Niger); Synergy of Civil Society Organizations (Niger); USN: Union of Nigerien Students ---- Students (Niger) ---- Students (Niger) ---- Students (Niger); USN: Union of Nigerien Students ---- ATN: Alliance of Workers of Niger; CDNT: Democratic Confederation of Workers of Niger; CNT: Nigerien Confederation of Labour; ITN: Inter-union of Workers of Niger; Labor Group (Niger); SYNACEB: National Union of Contract Agents and Basic Education Officers; UNSN: National Union of Trade Unions of Niger ---- Labor Group (Niger); UDTN: Democratic Union of Workers of Niger ---- Labor Group (Niger); Teachers (Niger); DSSEF: Education and Formation Trade Unions' Rally ---- DSSEF: Education and Formation Trade Unions' Rally; Labor Group (Niger); Students (Niger); Teachers (Niger); USN: Union of Nigerien Students ---- Students (Niger); USN: Union of Nigerien Students ---- Students (Niger)</t>
+        </is>
+      </c>
+      <c r="BI52" t="inlineStr">
+        <is>
+          <t>Civilians (Niger) ---- Civilians (Niger)</t>
+        </is>
+      </c>
+      <c r="BJ52" t="inlineStr">
+        <is>
+          <t>Muslim Group (Niger); Students (Niger); Teachers (Niger) ---- SNCES: National Union of Teacher-Researchers and Researchers of Higher Education; Students (Niger); Teachers (Niger)</t>
+        </is>
+      </c>
+      <c r="BK52" t="inlineStr">
+        <is>
+          <t>On 9 February 2024, the Union of Nigerien Students demonstrated in Niamey (Ville de Niamey, Niamey). They commemorated the 34th anniversary of the tragic events of February 9, 1990 which caused the death of three students. ---- On 29 April 2024, students including members of the USN staged a demonstration in Niamey (Ville de Niamey, Niamey). The organizer, the Union of Nigerien Students, demanded the unconditional departure of American troops from Niger. ---- On 16 November 2024, thousands of residents staged a demonstration in Niamey (Ville de Niamey, Niamey) to show their support to the CNSP. The organizer, the Synergy of Civil Society Organizations, joined by representants of Union of Nigerien Students, reaffirmed their adherence to the ideals of the CNSP, particularly in favor of national sovereignty and social stability. ---- On 11 February 2025, students protested in Niamey (Ville de Niamey, Niamey) to commemorate the 35th anniversary of the murder of three university students in the city and to demand that the government shed light on the incident and repair the damage caused. ---- On 21 February 2025, a students' union held a march in Niamey (Ville de Niamey, Niamey) in memory of a group of students from the University of Niamey killed during a peaceful protest in 1991 and to call on the authorities to pursue justice. ---- On 17 April 2025, militants of the Committee on Social Affairs and Order (CASO), linked with the Union of Nigerien Students (USN), beat up the vice-rector, a head of department, the university Imam and several students at the Islamic University of Niamey in Niamey (Ville de Niamey, Niamey). 4 students were injured and hospitalised. ---- On 1 May 2025, at the call of unions (ITN , SYNACEB, UNSN, ATN, CDNT and CNT), workers demonstrated in Niamey (Ville de Niamey, Niamey) to commemorate International Workers' Day. They called for the improvement of the working and living conditions for Niger's workers. They also expressed support for the Government of Niger, the Military Forces of Niger and for AES accusing France and other European countries of 'financing and training terrorists in the Sahel'. ---- Strikes: On 12 May 2025, the Education and Formation Trade Unions' Rally (DSSEF), a rally composed of 28 trade unions in the education and formation sector, called a national strike of three days, to demand the regular payment of their salaries, the immediate recruitment of education contractors to the public sector and the protection of the education personnel in conflict-affected areas. The UDTN supported DSSEF's demands and invited the Government of Niger to open a negotiation table. DSSEF's national strike comes after circumscribed mobilizations of education trade unions in Zinder, Torodi, Oullam and Sabon Machi. The strike ended without agreement, and the trade union delegate announced that 'new actions are not excluded if claims remain unsatisfied'. Location coded to the country's administrative capital Niamey (Ville de Niamey, Niamey). ---- Strikes: On 21 May 2025, the Education and Formation Trade Unions' Rally (DSSEF), a rally composed of 28 trade unions in the education and formation sector, called a national strike of three days, to demand the regular payment of their salaries, the immediate recruitment of education contractors to the public sector and the protection of the education personnel in conflict-affected areas. This strike follows another teachers' mobilization the previous week that ended without an agreement with the government. Location coded to the country's administrative capital Niamey (Ville de Niamey, Niamey). ---- Strikes: On 2 June 2025, the Education and Formation Trade Unions' Rally (DSSEF), a rally composed of 28 trade unions in the education and formation sector, called a national strike of five days to demand the regular payment of their salaries, the immediate recruitment of education contractors to the public sector and the protection of the education personnel in conflict-affected areas. This strike follows 2 other teachers' mobilizations over the previous weeks that ended without an agreement with the government. The Union of Nigerien Students (USN) urged the government to reach an agreement with the teachers to avoid further strikes and resume lectures. Location coded to the country's administrative capital, Niamey (Ville de Niamey, Niamey). ---- On 28 June 2025, militants of the Committee on Social Affairs and Order (CASO), linked with the Union of Nigerien Students (USN), violently interrupted the open day organised by the National Union of Teachers-Researchers and Researchers of higher education (SNCES) an the University of Niamey in Niamey (Ville de Niamey, Niamey), beting some researchers, destroying equipment and stealing a phone with the recordings of CASO's violent acts.No information on injuries. ---- On 18 July 2025, students of the School of Mines, of Industry and Geology (EMIG), kept their teachers, administrative and technical staff inside the school, locking the gates as a sign of protest in Niamey (Ville de Niamey, Niamey), because they did not align with the student unions' demands. Some were forced to climb over the wall to get back to their homes. They prevented them from attending Friday prayers. The student also blocked the road (means unspecified) leading to the university hospital.</t>
+        </is>
+      </c>
+      <c r="BL52" t="inlineStr">
+        <is>
+          <t>2024-02-09 ---- 2024-04-29 ---- 2024-11-16 ---- 2025-02-11 ---- 2025-02-21 ---- 2025-04-17 ---- 2025-05-01 ---- 2025-05-12 ---- 2025-05-21 ---- 2025-06-02 ---- 2025-06-28 ---- 2025-07-18</t>
+        </is>
+      </c>
+      <c r="BM52" t="inlineStr">
+        <is>
+          <t>Ville de Niamey</t>
+        </is>
+      </c>
+      <c r="BN52" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7373,13 +7671,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE5C6610-D3B5-409C-8A75-591ED873AC3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5077E399-B27E-4923-87FF-97CC7DB62559}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3594E97F-8102-4F75-B44D-F676BF6D94BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{406566AA-AFB4-4F5B-B858-F1F4F33DC10D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECC02CCA-8BD5-440E-AF16-40B365B5E442}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0389B546-C84A-444F-A859-6A0307099199}"/>
 </file>